--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R2" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R3" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B18" t="n">
-        <v>78725</v>
+        <v>78634</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R18" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B19" t="n">
-        <v>78634</v>
+        <v>78725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R19" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939285</v>
+        <v>125939283</v>
       </c>
       <c r="B20" t="n">
-        <v>77916</v>
+        <v>78634</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454930</v>
+        <v>454888</v>
       </c>
       <c r="R20" t="n">
-        <v>6811482</v>
+        <v>6811478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939283</v>
+        <v>125939238</v>
       </c>
       <c r="B21" t="n">
-        <v>78634</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,34 +2529,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454888</v>
+        <v>454804</v>
       </c>
       <c r="R21" t="n">
-        <v>6811478</v>
+        <v>6811564</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2578,7 +2583,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2589,6 +2594,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939238</v>
+        <v>125939285</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>77916</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,39 +2636,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454804</v>
+        <v>454930</v>
       </c>
       <c r="R22" t="n">
-        <v>6811564</v>
+        <v>6811482</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,7 +2685,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2691,11 +2696,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939228</v>
+        <v>125939221</v>
       </c>
       <c r="B30" t="n">
-        <v>79556</v>
+        <v>79585</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454892</v>
+        <v>454868</v>
       </c>
       <c r="R30" t="n">
-        <v>6811478</v>
+        <v>6811496</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939245</v>
+        <v>125939224</v>
       </c>
       <c r="B31" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454945</v>
+        <v>454899</v>
       </c>
       <c r="R31" t="n">
-        <v>6811496</v>
+        <v>6811425</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939221</v>
+        <v>125939228</v>
       </c>
       <c r="B32" t="n">
-        <v>79585</v>
+        <v>79556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454868</v>
+        <v>454892</v>
       </c>
       <c r="R32" t="n">
-        <v>6811496</v>
+        <v>6811478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939224</v>
+        <v>125939245</v>
       </c>
       <c r="B33" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454899</v>
+        <v>454945</v>
       </c>
       <c r="R33" t="n">
-        <v>6811425</v>
+        <v>6811496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939219</v>
+        <v>125939229</v>
       </c>
       <c r="B45" t="n">
-        <v>79585</v>
+        <v>79556</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454849</v>
+        <v>454945</v>
       </c>
       <c r="R45" t="n">
-        <v>6811570</v>
+        <v>6811496</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939257</v>
+        <v>125939219</v>
       </c>
       <c r="B46" t="n">
-        <v>78725</v>
+        <v>79585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454910</v>
+        <v>454849</v>
       </c>
       <c r="R46" t="n">
-        <v>6811442</v>
+        <v>6811570</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939264</v>
+        <v>125939257</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454788</v>
+        <v>454910</v>
       </c>
       <c r="R47" t="n">
-        <v>6811599</v>
+        <v>6811442</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5152,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125939229</v>
+        <v>125939264</v>
       </c>
       <c r="B48" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454945</v>
+        <v>454788</v>
       </c>
       <c r="R48" t="n">
-        <v>6811496</v>
+        <v>6811599</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939248</v>
+        <v>125939260</v>
       </c>
       <c r="B52" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454938</v>
+        <v>454706</v>
       </c>
       <c r="R52" t="n">
-        <v>6811339</v>
+        <v>6811484</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5734,7 +5734,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939260</v>
+        <v>125939271</v>
       </c>
       <c r="B54" t="n">
         <v>78967</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454706</v>
+        <v>454943</v>
       </c>
       <c r="R54" t="n">
-        <v>6811484</v>
+        <v>6811446</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5831,7 +5831,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939271</v>
+        <v>125939268</v>
       </c>
       <c r="B55" t="n">
         <v>78967</v>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454943</v>
+        <v>454882</v>
       </c>
       <c r="R55" t="n">
-        <v>6811446</v>
+        <v>6811551</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939268</v>
+        <v>125939248</v>
       </c>
       <c r="B56" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454882</v>
+        <v>454938</v>
       </c>
       <c r="R56" t="n">
-        <v>6811551</v>
+        <v>6811339</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125939272</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125939240</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939282</v>
+        <v>125939276</v>
       </c>
       <c r="B4" t="n">
-        <v>78634</v>
+        <v>92510</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454870</v>
+        <v>454947</v>
       </c>
       <c r="R4" t="n">
-        <v>6811495</v>
+        <v>6811454</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -929,7 +929,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B5" t="n">
-        <v>92509</v>
+        <v>78727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R5" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939247</v>
+        <v>125939282</v>
       </c>
       <c r="B6" t="n">
-        <v>78726</v>
+        <v>78635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454910</v>
+        <v>454870</v>
       </c>
       <c r="R6" t="n">
-        <v>6811441</v>
+        <v>6811495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125939256</v>
+        <v>125939217</v>
       </c>
       <c r="B7" t="n">
-        <v>78725</v>
+        <v>79586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454960</v>
+        <v>454837</v>
       </c>
       <c r="R7" t="n">
-        <v>6811451</v>
+        <v>6811351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939217</v>
+        <v>125939256</v>
       </c>
       <c r="B8" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454837</v>
+        <v>454960</v>
       </c>
       <c r="R8" t="n">
-        <v>6811351</v>
+        <v>6811451</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939278</v>
+        <v>125939286</v>
       </c>
       <c r="B9" t="n">
-        <v>78634</v>
+        <v>78374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454854</v>
+        <v>454835</v>
       </c>
       <c r="R9" t="n">
-        <v>6811347</v>
+        <v>6811352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939286</v>
+        <v>125939278</v>
       </c>
       <c r="B10" t="n">
-        <v>78373</v>
+        <v>78635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454835</v>
+        <v>454854</v>
       </c>
       <c r="R10" t="n">
-        <v>6811352</v>
+        <v>6811347</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939222</v>
+        <v>125939243</v>
       </c>
       <c r="B11" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454945</v>
+        <v>454896</v>
       </c>
       <c r="R11" t="n">
-        <v>6811496</v>
+        <v>6811477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939250</v>
+        <v>125939230</v>
       </c>
       <c r="B12" t="n">
-        <v>78725</v>
+        <v>79557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454931</v>
+        <v>454944</v>
       </c>
       <c r="R12" t="n">
-        <v>6811462</v>
+        <v>6811441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939253</v>
+        <v>125939277</v>
       </c>
       <c r="B13" t="n">
-        <v>78725</v>
+        <v>78635</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454880</v>
+        <v>454907</v>
       </c>
       <c r="R13" t="n">
-        <v>6811541</v>
+        <v>6811355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>125939223</v>
       </c>
       <c r="B14" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939277</v>
+        <v>125939250</v>
       </c>
       <c r="B15" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454907</v>
+        <v>454931</v>
       </c>
       <c r="R15" t="n">
-        <v>6811355</v>
+        <v>6811462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939243</v>
+        <v>125939222</v>
       </c>
       <c r="B16" t="n">
-        <v>78726</v>
+        <v>79586</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454896</v>
+        <v>454945</v>
       </c>
       <c r="R16" t="n">
-        <v>6811477</v>
+        <v>6811496</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939230</v>
+        <v>125939253</v>
       </c>
       <c r="B17" t="n">
-        <v>79556</v>
+        <v>78726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454944</v>
+        <v>454880</v>
       </c>
       <c r="R17" t="n">
-        <v>6811441</v>
+        <v>6811541</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
         <v>125939280</v>
       </c>
       <c r="B18" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>125939254</v>
       </c>
       <c r="B19" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>125939283</v>
       </c>
       <c r="B20" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125939285</v>
       </c>
       <c r="B22" t="n">
-        <v>77916</v>
+        <v>77917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>125939246</v>
       </c>
       <c r="B23" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939262</v>
+        <v>125939242</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454710</v>
+        <v>454883</v>
       </c>
       <c r="R24" t="n">
-        <v>6811492</v>
+        <v>6811548</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125939263</v>
+        <v>125939262</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454734</v>
+        <v>454710</v>
       </c>
       <c r="R25" t="n">
-        <v>6811565</v>
+        <v>6811492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939242</v>
+        <v>125939263</v>
       </c>
       <c r="B26" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454883</v>
+        <v>454734</v>
       </c>
       <c r="R26" t="n">
-        <v>6811548</v>
+        <v>6811565</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3215,7 +3215,7 @@
         <v>125939273</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>125939269</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939221</v>
+        <v>125939270</v>
       </c>
       <c r="B30" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454868</v>
+        <v>454944</v>
       </c>
       <c r="R30" t="n">
-        <v>6811496</v>
+        <v>6811442</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3506,7 +3506,7 @@
         <v>125939224</v>
       </c>
       <c r="B31" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939228</v>
+        <v>125939221</v>
       </c>
       <c r="B32" t="n">
-        <v>79556</v>
+        <v>79586</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454892</v>
+        <v>454868</v>
       </c>
       <c r="R32" t="n">
-        <v>6811478</v>
+        <v>6811496</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939245</v>
+        <v>125939231</v>
       </c>
       <c r="B33" t="n">
-        <v>78726</v>
+        <v>79063</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454945</v>
+        <v>454930</v>
       </c>
       <c r="R33" t="n">
-        <v>6811496</v>
+        <v>6811482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939231</v>
+        <v>125939281</v>
       </c>
       <c r="B34" t="n">
-        <v>79062</v>
+        <v>78635</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>967</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454930</v>
+        <v>454865</v>
       </c>
       <c r="R34" t="n">
-        <v>6811482</v>
+        <v>6811503</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939281</v>
+        <v>125939228</v>
       </c>
       <c r="B35" t="n">
-        <v>78634</v>
+        <v>79557</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454865</v>
+        <v>454892</v>
       </c>
       <c r="R35" t="n">
-        <v>6811503</v>
+        <v>6811478</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939270</v>
+        <v>125939245</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454944</v>
+        <v>454945</v>
       </c>
       <c r="R36" t="n">
-        <v>6811442</v>
+        <v>6811496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939226</v>
+        <v>125939241</v>
       </c>
       <c r="B37" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454938</v>
+        <v>454802</v>
       </c>
       <c r="R37" t="n">
-        <v>6811337</v>
+        <v>6811558</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939218</v>
+        <v>125939279</v>
       </c>
       <c r="B38" t="n">
-        <v>79585</v>
+        <v>78635</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454769</v>
+        <v>454802</v>
       </c>
       <c r="R38" t="n">
-        <v>6811673</v>
+        <v>6811557</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939279</v>
+        <v>125939218</v>
       </c>
       <c r="B39" t="n">
-        <v>78634</v>
+        <v>79586</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454802</v>
+        <v>454769</v>
       </c>
       <c r="R39" t="n">
-        <v>6811557</v>
+        <v>6811673</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>125939274</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>125939265</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939241</v>
+        <v>125939226</v>
       </c>
       <c r="B42" t="n">
-        <v>78726</v>
+        <v>79586</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454802</v>
+        <v>454938</v>
       </c>
       <c r="R42" t="n">
-        <v>6811558</v>
+        <v>6811337</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4670,7 +4670,7 @@
         <v>125939266</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>125939227</v>
       </c>
       <c r="B44" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939229</v>
+        <v>125939219</v>
       </c>
       <c r="B45" t="n">
-        <v>79556</v>
+        <v>79586</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454945</v>
+        <v>454849</v>
       </c>
       <c r="R45" t="n">
-        <v>6811496</v>
+        <v>6811570</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939219</v>
+        <v>125939264</v>
       </c>
       <c r="B46" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454849</v>
+        <v>454788</v>
       </c>
       <c r="R46" t="n">
-        <v>6811570</v>
+        <v>6811599</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5058,7 +5058,7 @@
         <v>125939257</v>
       </c>
       <c r="B47" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125939264</v>
+        <v>125939229</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>79557</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454788</v>
+        <v>454945</v>
       </c>
       <c r="R48" t="n">
-        <v>6811599</v>
+        <v>6811496</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B49" t="n">
-        <v>79585</v>
+        <v>78635</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R49" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B50" t="n">
-        <v>78634</v>
+        <v>79586</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R50" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5446,7 +5446,7 @@
         <v>125939267</v>
       </c>
       <c r="B51" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939260</v>
+        <v>125939248</v>
       </c>
       <c r="B52" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454706</v>
+        <v>454938</v>
       </c>
       <c r="R52" t="n">
-        <v>6811484</v>
+        <v>6811339</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939251</v>
+        <v>125939260</v>
       </c>
       <c r="B53" t="n">
-        <v>78725</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454806</v>
+        <v>454706</v>
       </c>
       <c r="R53" t="n">
-        <v>6811636</v>
+        <v>6811484</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939271</v>
+        <v>125939251</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5745,21 +5745,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454943</v>
+        <v>454806</v>
       </c>
       <c r="R54" t="n">
-        <v>6811446</v>
+        <v>6811636</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5831,10 +5831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939268</v>
+        <v>125939271</v>
       </c>
       <c r="B55" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454882</v>
+        <v>454943</v>
       </c>
       <c r="R55" t="n">
-        <v>6811551</v>
+        <v>6811446</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939248</v>
+        <v>125939268</v>
       </c>
       <c r="B56" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454938</v>
+        <v>454882</v>
       </c>
       <c r="R56" t="n">
-        <v>6811339</v>
+        <v>6811551</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B4" t="n">
-        <v>92510</v>
+        <v>78727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R4" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939247</v>
+        <v>125939282</v>
       </c>
       <c r="B5" t="n">
-        <v>78727</v>
+        <v>78635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454910</v>
+        <v>454870</v>
       </c>
       <c r="R5" t="n">
-        <v>6811441</v>
+        <v>6811495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939282</v>
+        <v>125939276</v>
       </c>
       <c r="B6" t="n">
-        <v>78635</v>
+        <v>92518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454870</v>
+        <v>454947</v>
       </c>
       <c r="R6" t="n">
-        <v>6811495</v>
+        <v>6811454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939243</v>
+        <v>125939223</v>
       </c>
       <c r="B11" t="n">
-        <v>78727</v>
+        <v>79586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454896</v>
+        <v>454961</v>
       </c>
       <c r="R11" t="n">
-        <v>6811477</v>
+        <v>6811450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939230</v>
+        <v>125939250</v>
       </c>
       <c r="B12" t="n">
-        <v>79557</v>
+        <v>78726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454944</v>
+        <v>454931</v>
       </c>
       <c r="R12" t="n">
-        <v>6811441</v>
+        <v>6811462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939277</v>
+        <v>125939222</v>
       </c>
       <c r="B13" t="n">
-        <v>78635</v>
+        <v>79586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454907</v>
+        <v>454945</v>
       </c>
       <c r="R13" t="n">
-        <v>6811355</v>
+        <v>6811496</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939223</v>
+        <v>125939253</v>
       </c>
       <c r="B14" t="n">
-        <v>79586</v>
+        <v>78726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454961</v>
+        <v>454880</v>
       </c>
       <c r="R14" t="n">
-        <v>6811450</v>
+        <v>6811541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939250</v>
+        <v>125939277</v>
       </c>
       <c r="B15" t="n">
-        <v>78726</v>
+        <v>78635</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454931</v>
+        <v>454907</v>
       </c>
       <c r="R15" t="n">
-        <v>6811462</v>
+        <v>6811355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939222</v>
+        <v>125939243</v>
       </c>
       <c r="B16" t="n">
-        <v>79586</v>
+        <v>78727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454945</v>
+        <v>454896</v>
       </c>
       <c r="R16" t="n">
-        <v>6811496</v>
+        <v>6811477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939253</v>
+        <v>125939230</v>
       </c>
       <c r="B17" t="n">
-        <v>78726</v>
+        <v>79557</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454880</v>
+        <v>454944</v>
       </c>
       <c r="R17" t="n">
-        <v>6811541</v>
+        <v>6811441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B18" t="n">
-        <v>78635</v>
+        <v>78726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R18" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B19" t="n">
-        <v>78726</v>
+        <v>78635</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R19" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939283</v>
+        <v>125939246</v>
       </c>
       <c r="B20" t="n">
-        <v>78635</v>
+        <v>78727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454888</v>
+        <v>454944</v>
       </c>
       <c r="R20" t="n">
-        <v>6811478</v>
+        <v>6811441</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939246</v>
+        <v>125939283</v>
       </c>
       <c r="B23" t="n">
-        <v>78727</v>
+        <v>78635</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454944</v>
+        <v>454888</v>
       </c>
       <c r="R23" t="n">
-        <v>6811441</v>
+        <v>6811478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939242</v>
+        <v>125939262</v>
       </c>
       <c r="B24" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454883</v>
+        <v>454710</v>
       </c>
       <c r="R24" t="n">
-        <v>6811548</v>
+        <v>6811492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125939262</v>
+        <v>125939263</v>
       </c>
       <c r="B25" t="n">
         <v>78968</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454710</v>
+        <v>454734</v>
       </c>
       <c r="R25" t="n">
-        <v>6811492</v>
+        <v>6811565</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,45 +3013,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939263</v>
+        <v>125939233</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454734</v>
+        <v>454794</v>
       </c>
       <c r="R26" t="n">
-        <v>6811565</v>
+        <v>6811612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,50 +3115,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125939233</v>
+        <v>125939242</v>
       </c>
       <c r="B27" t="n">
-        <v>56843</v>
+        <v>78727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454794</v>
+        <v>454883</v>
       </c>
       <c r="R27" t="n">
-        <v>6811612</v>
+        <v>6811548</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939270</v>
+        <v>125939228</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>79557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454944</v>
+        <v>454892</v>
       </c>
       <c r="R30" t="n">
-        <v>6811442</v>
+        <v>6811478</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939224</v>
+        <v>125939245</v>
       </c>
       <c r="B31" t="n">
-        <v>79586</v>
+        <v>78727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454899</v>
+        <v>454945</v>
       </c>
       <c r="R31" t="n">
-        <v>6811425</v>
+        <v>6811496</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939221</v>
+        <v>125939231</v>
       </c>
       <c r="B32" t="n">
-        <v>79586</v>
+        <v>79063</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454868</v>
+        <v>454930</v>
       </c>
       <c r="R32" t="n">
-        <v>6811496</v>
+        <v>6811482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939231</v>
+        <v>125939281</v>
       </c>
       <c r="B33" t="n">
-        <v>79063</v>
+        <v>78635</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>967</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454930</v>
+        <v>454865</v>
       </c>
       <c r="R33" t="n">
-        <v>6811482</v>
+        <v>6811503</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939281</v>
+        <v>125939270</v>
       </c>
       <c r="B34" t="n">
-        <v>78635</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454865</v>
+        <v>454944</v>
       </c>
       <c r="R34" t="n">
-        <v>6811503</v>
+        <v>6811442</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939228</v>
+        <v>125939224</v>
       </c>
       <c r="B35" t="n">
-        <v>79557</v>
+        <v>79586</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454892</v>
+        <v>454899</v>
       </c>
       <c r="R35" t="n">
-        <v>6811478</v>
+        <v>6811425</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939245</v>
+        <v>125939221</v>
       </c>
       <c r="B36" t="n">
-        <v>78727</v>
+        <v>79586</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454945</v>
+        <v>454868</v>
       </c>
       <c r="R36" t="n">
         <v>6811496</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939241</v>
+        <v>125939218</v>
       </c>
       <c r="B37" t="n">
-        <v>78727</v>
+        <v>79586</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454802</v>
+        <v>454769</v>
       </c>
       <c r="R37" t="n">
-        <v>6811558</v>
+        <v>6811673</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939279</v>
+        <v>125939274</v>
       </c>
       <c r="B38" t="n">
-        <v>78635</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454802</v>
+        <v>454933</v>
       </c>
       <c r="R38" t="n">
-        <v>6811557</v>
+        <v>6811343</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939218</v>
+        <v>125939265</v>
       </c>
       <c r="B39" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454769</v>
+        <v>454793</v>
       </c>
       <c r="R39" t="n">
-        <v>6811673</v>
+        <v>6811562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939274</v>
+        <v>125939226</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454933</v>
+        <v>454938</v>
       </c>
       <c r="R40" t="n">
-        <v>6811343</v>
+        <v>6811337</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939265</v>
+        <v>125939279</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>78635</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454793</v>
+        <v>454802</v>
       </c>
       <c r="R41" t="n">
-        <v>6811562</v>
+        <v>6811557</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939226</v>
+        <v>125939241</v>
       </c>
       <c r="B42" t="n">
-        <v>79586</v>
+        <v>78727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454938</v>
+        <v>454802</v>
       </c>
       <c r="R42" t="n">
-        <v>6811337</v>
+        <v>6811558</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B49" t="n">
-        <v>78635</v>
+        <v>79586</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R49" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B50" t="n">
-        <v>79586</v>
+        <v>78635</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R50" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939248</v>
+        <v>125939260</v>
       </c>
       <c r="B52" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454938</v>
+        <v>454706</v>
       </c>
       <c r="R52" t="n">
-        <v>6811339</v>
+        <v>6811484</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939260</v>
+        <v>125939251</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>78726</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454706</v>
+        <v>454806</v>
       </c>
       <c r="R53" t="n">
-        <v>6811484</v>
+        <v>6811636</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939251</v>
+        <v>125939271</v>
       </c>
       <c r="B54" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5745,21 +5745,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454806</v>
+        <v>454943</v>
       </c>
       <c r="R54" t="n">
-        <v>6811636</v>
+        <v>6811446</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5831,7 +5831,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939271</v>
+        <v>125939268</v>
       </c>
       <c r="B55" t="n">
         <v>78968</v>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454943</v>
+        <v>454882</v>
       </c>
       <c r="R55" t="n">
-        <v>6811446</v>
+        <v>6811551</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939268</v>
+        <v>125939248</v>
       </c>
       <c r="B56" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454882</v>
+        <v>454938</v>
       </c>
       <c r="R56" t="n">
-        <v>6811551</v>
+        <v>6811339</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939285</v>
+        <v>125939283</v>
       </c>
       <c r="B22" t="n">
-        <v>77917</v>
+        <v>78635</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454930</v>
+        <v>454888</v>
       </c>
       <c r="R22" t="n">
-        <v>6811482</v>
+        <v>6811478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939283</v>
+        <v>125939285</v>
       </c>
       <c r="B23" t="n">
-        <v>78635</v>
+        <v>77917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454888</v>
+        <v>454930</v>
       </c>
       <c r="R23" t="n">
-        <v>6811478</v>
+        <v>6811482</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939262</v>
+        <v>125939242</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454710</v>
+        <v>454883</v>
       </c>
       <c r="R24" t="n">
-        <v>6811492</v>
+        <v>6811548</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125939263</v>
+        <v>125939262</v>
       </c>
       <c r="B25" t="n">
         <v>78968</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454734</v>
+        <v>454710</v>
       </c>
       <c r="R25" t="n">
-        <v>6811565</v>
+        <v>6811492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,50 +3013,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939233</v>
+        <v>125939263</v>
       </c>
       <c r="B26" t="n">
-        <v>56843</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454794</v>
+        <v>454734</v>
       </c>
       <c r="R26" t="n">
-        <v>6811612</v>
+        <v>6811565</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3115,45 +3110,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125939242</v>
+        <v>125939233</v>
       </c>
       <c r="B27" t="n">
-        <v>78727</v>
+        <v>56843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454883</v>
+        <v>454794</v>
       </c>
       <c r="R27" t="n">
-        <v>6811548</v>
+        <v>6811612</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939228</v>
+        <v>125939231</v>
       </c>
       <c r="B30" t="n">
-        <v>79557</v>
+        <v>79063</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454892</v>
+        <v>454930</v>
       </c>
       <c r="R30" t="n">
-        <v>6811478</v>
+        <v>6811482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939245</v>
+        <v>125939281</v>
       </c>
       <c r="B31" t="n">
-        <v>78727</v>
+        <v>78635</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454945</v>
+        <v>454865</v>
       </c>
       <c r="R31" t="n">
-        <v>6811496</v>
+        <v>6811503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939231</v>
+        <v>125939228</v>
       </c>
       <c r="B32" t="n">
-        <v>79063</v>
+        <v>79557</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454930</v>
+        <v>454892</v>
       </c>
       <c r="R32" t="n">
-        <v>6811482</v>
+        <v>6811478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939281</v>
+        <v>125939245</v>
       </c>
       <c r="B33" t="n">
-        <v>78635</v>
+        <v>78727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454865</v>
+        <v>454945</v>
       </c>
       <c r="R33" t="n">
-        <v>6811503</v>
+        <v>6811496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939219</v>
+        <v>125939229</v>
       </c>
       <c r="B45" t="n">
-        <v>79586</v>
+        <v>79557</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454849</v>
+        <v>454945</v>
       </c>
       <c r="R45" t="n">
-        <v>6811570</v>
+        <v>6811496</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939264</v>
+        <v>125939219</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454788</v>
+        <v>454849</v>
       </c>
       <c r="R46" t="n">
-        <v>6811599</v>
+        <v>6811570</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939257</v>
+        <v>125939264</v>
       </c>
       <c r="B47" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454910</v>
+        <v>454788</v>
       </c>
       <c r="R47" t="n">
-        <v>6811442</v>
+        <v>6811599</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5152,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125939229</v>
+        <v>125939257</v>
       </c>
       <c r="B48" t="n">
-        <v>79557</v>
+        <v>78726</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454945</v>
+        <v>454910</v>
       </c>
       <c r="R48" t="n">
-        <v>6811496</v>
+        <v>6811442</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R2" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B3" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R3" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939247</v>
+        <v>125939276</v>
       </c>
       <c r="B4" t="n">
-        <v>78727</v>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454910</v>
+        <v>454947</v>
       </c>
       <c r="R4" t="n">
-        <v>6811441</v>
+        <v>6811454</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>125939282</v>
       </c>
       <c r="B5" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B6" t="n">
-        <v>92518</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R6" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>125939217</v>
       </c>
       <c r="B7" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125939256</v>
       </c>
       <c r="B8" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939286</v>
+        <v>125939278</v>
       </c>
       <c r="B9" t="n">
-        <v>78374</v>
+        <v>78639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454835</v>
+        <v>454854</v>
       </c>
       <c r="R9" t="n">
-        <v>6811352</v>
+        <v>6811347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939278</v>
+        <v>125939286</v>
       </c>
       <c r="B10" t="n">
-        <v>78635</v>
+        <v>78378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454854</v>
+        <v>454835</v>
       </c>
       <c r="R10" t="n">
-        <v>6811347</v>
+        <v>6811352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939223</v>
+        <v>125939243</v>
       </c>
       <c r="B11" t="n">
-        <v>79586</v>
+        <v>78731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454961</v>
+        <v>454896</v>
       </c>
       <c r="R11" t="n">
-        <v>6811450</v>
+        <v>6811477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939250</v>
+        <v>125939230</v>
       </c>
       <c r="B12" t="n">
-        <v>78726</v>
+        <v>79561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454931</v>
+        <v>454944</v>
       </c>
       <c r="R12" t="n">
-        <v>6811462</v>
+        <v>6811441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939222</v>
+        <v>125939223</v>
       </c>
       <c r="B13" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454945</v>
+        <v>454961</v>
       </c>
       <c r="R13" t="n">
-        <v>6811496</v>
+        <v>6811450</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939253</v>
+        <v>125939250</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454880</v>
+        <v>454931</v>
       </c>
       <c r="R14" t="n">
-        <v>6811541</v>
+        <v>6811462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939277</v>
+        <v>125939222</v>
       </c>
       <c r="B15" t="n">
-        <v>78635</v>
+        <v>79590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454907</v>
+        <v>454945</v>
       </c>
       <c r="R15" t="n">
-        <v>6811355</v>
+        <v>6811496</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939243</v>
+        <v>125939253</v>
       </c>
       <c r="B16" t="n">
-        <v>78727</v>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454896</v>
+        <v>454880</v>
       </c>
       <c r="R16" t="n">
-        <v>6811477</v>
+        <v>6811541</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939230</v>
+        <v>125939277</v>
       </c>
       <c r="B17" t="n">
-        <v>79557</v>
+        <v>78639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454944</v>
+        <v>454907</v>
       </c>
       <c r="R17" t="n">
-        <v>6811441</v>
+        <v>6811355</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B18" t="n">
-        <v>78726</v>
+        <v>78639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R18" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B19" t="n">
-        <v>78635</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R19" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939246</v>
+        <v>125939283</v>
       </c>
       <c r="B20" t="n">
-        <v>78727</v>
+        <v>78639</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454944</v>
+        <v>454888</v>
       </c>
       <c r="R20" t="n">
-        <v>6811441</v>
+        <v>6811478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939238</v>
+        <v>125939285</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>77921</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,39 +2529,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454804</v>
+        <v>454930</v>
       </c>
       <c r="R21" t="n">
-        <v>6811564</v>
+        <v>6811482</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,7 +2578,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2594,11 +2589,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2625,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939283</v>
+        <v>125939238</v>
       </c>
       <c r="B22" t="n">
-        <v>78635</v>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,34 +2626,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454888</v>
+        <v>454804</v>
       </c>
       <c r="R22" t="n">
-        <v>6811478</v>
+        <v>6811564</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,7 +2680,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2696,6 +2691,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939285</v>
+        <v>125939246</v>
       </c>
       <c r="B23" t="n">
-        <v>77917</v>
+        <v>78731</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454930</v>
+        <v>454944</v>
       </c>
       <c r="R23" t="n">
-        <v>6811482</v>
+        <v>6811441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939242</v>
+        <v>125939262</v>
       </c>
       <c r="B24" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454883</v>
+        <v>454710</v>
       </c>
       <c r="R24" t="n">
-        <v>6811548</v>
+        <v>6811492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125939262</v>
+        <v>125939263</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454710</v>
+        <v>454734</v>
       </c>
       <c r="R25" t="n">
-        <v>6811492</v>
+        <v>6811565</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,45 +3013,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939263</v>
+        <v>125939233</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454734</v>
+        <v>454794</v>
       </c>
       <c r="R26" t="n">
-        <v>6811565</v>
+        <v>6811612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,50 +3115,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125939233</v>
+        <v>125939242</v>
       </c>
       <c r="B27" t="n">
-        <v>56843</v>
+        <v>78731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454794</v>
+        <v>454883</v>
       </c>
       <c r="R27" t="n">
-        <v>6811612</v>
+        <v>6811548</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3215,7 +3215,7 @@
         <v>125939273</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>125939269</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939231</v>
+        <v>125939270</v>
       </c>
       <c r="B30" t="n">
-        <v>79063</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454930</v>
+        <v>454944</v>
       </c>
       <c r="R30" t="n">
-        <v>6811482</v>
+        <v>6811442</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939281</v>
+        <v>125939224</v>
       </c>
       <c r="B31" t="n">
-        <v>78635</v>
+        <v>79590</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454865</v>
+        <v>454899</v>
       </c>
       <c r="R31" t="n">
-        <v>6811503</v>
+        <v>6811425</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939228</v>
+        <v>125939221</v>
       </c>
       <c r="B32" t="n">
-        <v>79557</v>
+        <v>79590</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454892</v>
+        <v>454868</v>
       </c>
       <c r="R32" t="n">
-        <v>6811478</v>
+        <v>6811496</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939245</v>
+        <v>125939231</v>
       </c>
       <c r="B33" t="n">
-        <v>78727</v>
+        <v>79067</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454945</v>
+        <v>454930</v>
       </c>
       <c r="R33" t="n">
-        <v>6811496</v>
+        <v>6811482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939270</v>
+        <v>125939281</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454944</v>
+        <v>454865</v>
       </c>
       <c r="R34" t="n">
-        <v>6811442</v>
+        <v>6811503</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939224</v>
+        <v>125939228</v>
       </c>
       <c r="B35" t="n">
-        <v>79586</v>
+        <v>79561</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454899</v>
+        <v>454892</v>
       </c>
       <c r="R35" t="n">
-        <v>6811425</v>
+        <v>6811478</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939221</v>
+        <v>125939245</v>
       </c>
       <c r="B36" t="n">
-        <v>79586</v>
+        <v>78731</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454868</v>
+        <v>454945</v>
       </c>
       <c r="R36" t="n">
         <v>6811496</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939218</v>
+        <v>125939274</v>
       </c>
       <c r="B37" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454769</v>
+        <v>454933</v>
       </c>
       <c r="R37" t="n">
-        <v>6811673</v>
+        <v>6811343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939274</v>
+        <v>125939265</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454933</v>
+        <v>454793</v>
       </c>
       <c r="R38" t="n">
-        <v>6811343</v>
+        <v>6811562</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939265</v>
+        <v>125939218</v>
       </c>
       <c r="B39" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454793</v>
+        <v>454769</v>
       </c>
       <c r="R39" t="n">
-        <v>6811562</v>
+        <v>6811673</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>125939226</v>
       </c>
       <c r="B40" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>125939279</v>
       </c>
       <c r="B41" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>125939241</v>
       </c>
       <c r="B42" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>125939266</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>125939227</v>
       </c>
       <c r="B44" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>125939229</v>
       </c>
       <c r="B45" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939219</v>
+        <v>125939264</v>
       </c>
       <c r="B46" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454849</v>
+        <v>454788</v>
       </c>
       <c r="R46" t="n">
-        <v>6811570</v>
+        <v>6811599</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939264</v>
+        <v>125939219</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454788</v>
+        <v>454849</v>
       </c>
       <c r="R47" t="n">
-        <v>6811599</v>
+        <v>6811570</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
         <v>125939257</v>
       </c>
       <c r="B48" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B49" t="n">
-        <v>79586</v>
+        <v>78639</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R49" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B50" t="n">
-        <v>78635</v>
+        <v>79590</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R50" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5446,7 +5446,7 @@
         <v>125939267</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939260</v>
+        <v>125939251</v>
       </c>
       <c r="B52" t="n">
-        <v>78968</v>
+        <v>78730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454706</v>
+        <v>454806</v>
       </c>
       <c r="R52" t="n">
-        <v>6811484</v>
+        <v>6811636</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939251</v>
+        <v>125939271</v>
       </c>
       <c r="B53" t="n">
-        <v>78726</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454806</v>
+        <v>454943</v>
       </c>
       <c r="R53" t="n">
-        <v>6811636</v>
+        <v>6811446</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5734,10 +5734,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939271</v>
+        <v>125939268</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454943</v>
+        <v>454882</v>
       </c>
       <c r="R54" t="n">
-        <v>6811446</v>
+        <v>6811551</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5831,10 +5831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939268</v>
+        <v>125939248</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5842,21 +5842,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454882</v>
+        <v>454938</v>
       </c>
       <c r="R55" t="n">
-        <v>6811551</v>
+        <v>6811339</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939248</v>
+        <v>125939260</v>
       </c>
       <c r="B56" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454938</v>
+        <v>454706</v>
       </c>
       <c r="R56" t="n">
-        <v>6811339</v>
+        <v>6811484</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939278</v>
+        <v>125939286</v>
       </c>
       <c r="B9" t="n">
-        <v>78639</v>
+        <v>78378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454854</v>
+        <v>454835</v>
       </c>
       <c r="R9" t="n">
-        <v>6811347</v>
+        <v>6811352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939286</v>
+        <v>125939278</v>
       </c>
       <c r="B10" t="n">
-        <v>78378</v>
+        <v>78639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454835</v>
+        <v>454854</v>
       </c>
       <c r="R10" t="n">
-        <v>6811352</v>
+        <v>6811347</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939283</v>
+        <v>125939285</v>
       </c>
       <c r="B20" t="n">
-        <v>78639</v>
+        <v>77921</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454888</v>
+        <v>454930</v>
       </c>
       <c r="R20" t="n">
-        <v>6811478</v>
+        <v>6811482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939285</v>
+        <v>125939238</v>
       </c>
       <c r="B21" t="n">
-        <v>77921</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,34 +2529,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454930</v>
+        <v>454804</v>
       </c>
       <c r="R21" t="n">
-        <v>6811482</v>
+        <v>6811564</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2578,7 +2583,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2589,6 +2594,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939238</v>
+        <v>125939246</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,39 +2636,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454804</v>
+        <v>454944</v>
       </c>
       <c r="R22" t="n">
-        <v>6811564</v>
+        <v>6811441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,7 +2685,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2691,11 +2696,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939246</v>
+        <v>125939283</v>
       </c>
       <c r="B23" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454944</v>
+        <v>454888</v>
       </c>
       <c r="R23" t="n">
-        <v>6811441</v>
+        <v>6811478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,50 +3013,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939233</v>
+        <v>125939242</v>
       </c>
       <c r="B26" t="n">
-        <v>56843</v>
+        <v>78731</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454794</v>
+        <v>454883</v>
       </c>
       <c r="R26" t="n">
-        <v>6811612</v>
+        <v>6811548</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3078,7 +3073,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3115,45 +3110,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125939242</v>
+        <v>125939233</v>
       </c>
       <c r="B27" t="n">
-        <v>78731</v>
+        <v>56843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454883</v>
+        <v>454794</v>
       </c>
       <c r="R27" t="n">
-        <v>6811548</v>
+        <v>6811612</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939229</v>
+        <v>125939219</v>
       </c>
       <c r="B45" t="n">
-        <v>79561</v>
+        <v>79590</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454945</v>
+        <v>454849</v>
       </c>
       <c r="R45" t="n">
-        <v>6811496</v>
+        <v>6811570</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939264</v>
+        <v>125939257</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454788</v>
+        <v>454910</v>
       </c>
       <c r="R46" t="n">
-        <v>6811599</v>
+        <v>6811442</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939219</v>
+        <v>125939264</v>
       </c>
       <c r="B47" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454849</v>
+        <v>454788</v>
       </c>
       <c r="R47" t="n">
-        <v>6811570</v>
+        <v>6811599</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125939257</v>
+        <v>125939229</v>
       </c>
       <c r="B48" t="n">
-        <v>78730</v>
+        <v>79561</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454910</v>
+        <v>454945</v>
       </c>
       <c r="R48" t="n">
-        <v>6811442</v>
+        <v>6811496</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B49" t="n">
-        <v>78639</v>
+        <v>79590</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R49" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B50" t="n">
-        <v>79590</v>
+        <v>78639</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R50" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939251</v>
+        <v>125939248</v>
       </c>
       <c r="B52" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454806</v>
+        <v>454938</v>
       </c>
       <c r="R52" t="n">
-        <v>6811636</v>
+        <v>6811339</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939271</v>
+        <v>125939251</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454943</v>
+        <v>454806</v>
       </c>
       <c r="R53" t="n">
-        <v>6811446</v>
+        <v>6811636</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5734,7 +5734,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939268</v>
+        <v>125939260</v>
       </c>
       <c r="B54" t="n">
         <v>78972</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454882</v>
+        <v>454706</v>
       </c>
       <c r="R54" t="n">
-        <v>6811551</v>
+        <v>6811484</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5831,10 +5831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939248</v>
+        <v>125939271</v>
       </c>
       <c r="B55" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5842,21 +5842,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454938</v>
+        <v>454943</v>
       </c>
       <c r="R55" t="n">
-        <v>6811339</v>
+        <v>6811446</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5928,7 +5928,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939260</v>
+        <v>125939268</v>
       </c>
       <c r="B56" t="n">
         <v>78972</v>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454706</v>
+        <v>454882</v>
       </c>
       <c r="R56" t="n">
-        <v>6811484</v>
+        <v>6811551</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R2" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R3" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B4" t="n">
-        <v>92522</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R4" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939247</v>
+        <v>125939276</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454910</v>
+        <v>454947</v>
       </c>
       <c r="R6" t="n">
-        <v>6811441</v>
+        <v>6811454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939286</v>
+        <v>125939278</v>
       </c>
       <c r="B9" t="n">
-        <v>78378</v>
+        <v>78639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454835</v>
+        <v>454854</v>
       </c>
       <c r="R9" t="n">
-        <v>6811352</v>
+        <v>6811347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939278</v>
+        <v>125939286</v>
       </c>
       <c r="B10" t="n">
-        <v>78639</v>
+        <v>78378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454854</v>
+        <v>454835</v>
       </c>
       <c r="R10" t="n">
-        <v>6811347</v>
+        <v>6811352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939243</v>
+        <v>125939277</v>
       </c>
       <c r="B11" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454896</v>
+        <v>454907</v>
       </c>
       <c r="R11" t="n">
-        <v>6811477</v>
+        <v>6811355</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939230</v>
+        <v>125939223</v>
       </c>
       <c r="B12" t="n">
-        <v>79561</v>
+        <v>79590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454944</v>
+        <v>454961</v>
       </c>
       <c r="R12" t="n">
-        <v>6811441</v>
+        <v>6811450</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939223</v>
+        <v>125939250</v>
       </c>
       <c r="B13" t="n">
-        <v>79590</v>
+        <v>78730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454961</v>
+        <v>454931</v>
       </c>
       <c r="R13" t="n">
-        <v>6811450</v>
+        <v>6811462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939250</v>
+        <v>125939222</v>
       </c>
       <c r="B14" t="n">
-        <v>78730</v>
+        <v>79590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454931</v>
+        <v>454945</v>
       </c>
       <c r="R14" t="n">
-        <v>6811462</v>
+        <v>6811496</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939222</v>
+        <v>125939253</v>
       </c>
       <c r="B15" t="n">
-        <v>79590</v>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454945</v>
+        <v>454880</v>
       </c>
       <c r="R15" t="n">
-        <v>6811496</v>
+        <v>6811541</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939253</v>
+        <v>125939243</v>
       </c>
       <c r="B16" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454880</v>
+        <v>454896</v>
       </c>
       <c r="R16" t="n">
-        <v>6811541</v>
+        <v>6811477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939277</v>
+        <v>125939230</v>
       </c>
       <c r="B17" t="n">
-        <v>78639</v>
+        <v>79561</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454907</v>
+        <v>454944</v>
       </c>
       <c r="R17" t="n">
-        <v>6811355</v>
+        <v>6811441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3013,45 +3013,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939242</v>
+        <v>125939233</v>
       </c>
       <c r="B26" t="n">
-        <v>78731</v>
+        <v>56843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454883</v>
+        <v>454794</v>
       </c>
       <c r="R26" t="n">
-        <v>6811548</v>
+        <v>6811612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,7 +3078,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3110,50 +3115,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125939233</v>
+        <v>125939242</v>
       </c>
       <c r="B27" t="n">
-        <v>56843</v>
+        <v>78731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454794</v>
+        <v>454883</v>
       </c>
       <c r="R27" t="n">
-        <v>6811612</v>
+        <v>6811548</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939270</v>
+        <v>125939281</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454944</v>
+        <v>454865</v>
       </c>
       <c r="R30" t="n">
-        <v>6811442</v>
+        <v>6811503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939224</v>
+        <v>125939270</v>
       </c>
       <c r="B31" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454899</v>
+        <v>454944</v>
       </c>
       <c r="R31" t="n">
-        <v>6811425</v>
+        <v>6811442</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939221</v>
+        <v>125939231</v>
       </c>
       <c r="B32" t="n">
-        <v>79590</v>
+        <v>79067</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454868</v>
+        <v>454930</v>
       </c>
       <c r="R32" t="n">
-        <v>6811496</v>
+        <v>6811482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939231</v>
+        <v>125939224</v>
       </c>
       <c r="B33" t="n">
-        <v>79067</v>
+        <v>79590</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454930</v>
+        <v>454899</v>
       </c>
       <c r="R33" t="n">
-        <v>6811482</v>
+        <v>6811425</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939281</v>
+        <v>125939221</v>
       </c>
       <c r="B34" t="n">
-        <v>78639</v>
+        <v>79590</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454865</v>
+        <v>454868</v>
       </c>
       <c r="R34" t="n">
-        <v>6811503</v>
+        <v>6811496</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939218</v>
+        <v>125939241</v>
       </c>
       <c r="B39" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454769</v>
+        <v>454802</v>
       </c>
       <c r="R39" t="n">
-        <v>6811673</v>
+        <v>6811558</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939226</v>
+        <v>125939279</v>
       </c>
       <c r="B40" t="n">
-        <v>79590</v>
+        <v>78639</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454938</v>
+        <v>454802</v>
       </c>
       <c r="R40" t="n">
-        <v>6811337</v>
+        <v>6811557</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939279</v>
+        <v>125939218</v>
       </c>
       <c r="B41" t="n">
-        <v>78639</v>
+        <v>79590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454802</v>
+        <v>454769</v>
       </c>
       <c r="R41" t="n">
-        <v>6811557</v>
+        <v>6811673</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939241</v>
+        <v>125939226</v>
       </c>
       <c r="B42" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454802</v>
+        <v>454938</v>
       </c>
       <c r="R42" t="n">
-        <v>6811558</v>
+        <v>6811337</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939219</v>
+        <v>125939264</v>
       </c>
       <c r="B45" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454849</v>
+        <v>454788</v>
       </c>
       <c r="R45" t="n">
-        <v>6811570</v>
+        <v>6811599</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939257</v>
+        <v>125939219</v>
       </c>
       <c r="B46" t="n">
-        <v>78730</v>
+        <v>79590</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454910</v>
+        <v>454849</v>
       </c>
       <c r="R46" t="n">
-        <v>6811442</v>
+        <v>6811570</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939264</v>
+        <v>125939257</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454788</v>
+        <v>454910</v>
       </c>
       <c r="R47" t="n">
-        <v>6811599</v>
+        <v>6811442</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B49" t="n">
-        <v>79590</v>
+        <v>78639</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R49" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B50" t="n">
-        <v>78639</v>
+        <v>79590</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R50" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939248</v>
+        <v>125939260</v>
       </c>
       <c r="B52" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454938</v>
+        <v>454706</v>
       </c>
       <c r="R52" t="n">
-        <v>6811339</v>
+        <v>6811484</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939251</v>
+        <v>125939271</v>
       </c>
       <c r="B53" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454806</v>
+        <v>454943</v>
       </c>
       <c r="R53" t="n">
-        <v>6811636</v>
+        <v>6811446</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5734,7 +5734,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939260</v>
+        <v>125939268</v>
       </c>
       <c r="B54" t="n">
         <v>78972</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454706</v>
+        <v>454882</v>
       </c>
       <c r="R54" t="n">
-        <v>6811484</v>
+        <v>6811551</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5831,10 +5831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939271</v>
+        <v>125939251</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5842,21 +5842,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454943</v>
+        <v>454806</v>
       </c>
       <c r="R55" t="n">
-        <v>6811446</v>
+        <v>6811636</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -5928,10 +5928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939268</v>
+        <v>125939248</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454882</v>
+        <v>454938</v>
       </c>
       <c r="R56" t="n">
-        <v>6811551</v>
+        <v>6811339</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R2" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R3" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939282</v>
+        <v>125939276</v>
       </c>
       <c r="B5" t="n">
-        <v>78639</v>
+        <v>92522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454870</v>
+        <v>454947</v>
       </c>
       <c r="R5" t="n">
-        <v>6811495</v>
+        <v>6811454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939276</v>
+        <v>125939282</v>
       </c>
       <c r="B6" t="n">
-        <v>92522</v>
+        <v>78639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454947</v>
+        <v>454870</v>
       </c>
       <c r="R6" t="n">
-        <v>6811454</v>
+        <v>6811495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B18" t="n">
-        <v>78639</v>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R18" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>78639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R19" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939285</v>
+        <v>125939246</v>
       </c>
       <c r="B20" t="n">
-        <v>77921</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454930</v>
+        <v>454944</v>
       </c>
       <c r="R20" t="n">
-        <v>6811482</v>
+        <v>6811441</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939238</v>
+        <v>125939283</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>78639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,39 +2529,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454804</v>
+        <v>454888</v>
       </c>
       <c r="R21" t="n">
-        <v>6811564</v>
+        <v>6811478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,7 +2578,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2594,11 +2589,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2625,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939246</v>
+        <v>125939285</v>
       </c>
       <c r="B22" t="n">
-        <v>78731</v>
+        <v>77921</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454944</v>
+        <v>454930</v>
       </c>
       <c r="R22" t="n">
-        <v>6811441</v>
+        <v>6811482</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939283</v>
+        <v>125939238</v>
       </c>
       <c r="B23" t="n">
-        <v>78639</v>
+        <v>57651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,34 +2723,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454888</v>
+        <v>454804</v>
       </c>
       <c r="R23" t="n">
-        <v>6811478</v>
+        <v>6811564</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,7 +2777,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2793,6 +2788,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5637,7 +5637,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939271</v>
+        <v>125939268</v>
       </c>
       <c r="B53" t="n">
         <v>78972</v>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454943</v>
+        <v>454882</v>
       </c>
       <c r="R53" t="n">
-        <v>6811446</v>
+        <v>6811551</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939268</v>
+        <v>125939271</v>
       </c>
       <c r="B54" t="n">
         <v>78972</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454882</v>
+        <v>454943</v>
       </c>
       <c r="R54" t="n">
-        <v>6811551</v>
+        <v>6811446</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939276</v>
+        <v>125939282</v>
       </c>
       <c r="B5" t="n">
-        <v>92522</v>
+        <v>78639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454947</v>
+        <v>454870</v>
       </c>
       <c r="R5" t="n">
-        <v>6811454</v>
+        <v>6811495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939282</v>
+        <v>125939276</v>
       </c>
       <c r="B6" t="n">
-        <v>78639</v>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454870</v>
+        <v>454947</v>
       </c>
       <c r="R6" t="n">
-        <v>6811495</v>
+        <v>6811454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939277</v>
+        <v>125939223</v>
       </c>
       <c r="B11" t="n">
-        <v>78639</v>
+        <v>79590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454907</v>
+        <v>454961</v>
       </c>
       <c r="R11" t="n">
-        <v>6811355</v>
+        <v>6811450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939223</v>
+        <v>125939250</v>
       </c>
       <c r="B12" t="n">
-        <v>79590</v>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454961</v>
+        <v>454931</v>
       </c>
       <c r="R12" t="n">
-        <v>6811450</v>
+        <v>6811462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939250</v>
+        <v>125939222</v>
       </c>
       <c r="B13" t="n">
-        <v>78730</v>
+        <v>79590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454931</v>
+        <v>454945</v>
       </c>
       <c r="R13" t="n">
-        <v>6811462</v>
+        <v>6811496</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939222</v>
+        <v>125939253</v>
       </c>
       <c r="B14" t="n">
-        <v>79590</v>
+        <v>78730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454945</v>
+        <v>454880</v>
       </c>
       <c r="R14" t="n">
-        <v>6811496</v>
+        <v>6811541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939253</v>
+        <v>125939243</v>
       </c>
       <c r="B15" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454880</v>
+        <v>454896</v>
       </c>
       <c r="R15" t="n">
-        <v>6811541</v>
+        <v>6811477</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939243</v>
+        <v>125939230</v>
       </c>
       <c r="B16" t="n">
-        <v>78731</v>
+        <v>79561</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454896</v>
+        <v>454944</v>
       </c>
       <c r="R16" t="n">
-        <v>6811477</v>
+        <v>6811441</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939230</v>
+        <v>125939277</v>
       </c>
       <c r="B17" t="n">
-        <v>79561</v>
+        <v>78639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454944</v>
+        <v>454907</v>
       </c>
       <c r="R17" t="n">
-        <v>6811441</v>
+        <v>6811355</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B18" t="n">
-        <v>78730</v>
+        <v>78639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R18" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B19" t="n">
-        <v>78639</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R19" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939246</v>
+        <v>125939285</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>77921</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454944</v>
+        <v>454930</v>
       </c>
       <c r="R20" t="n">
-        <v>6811441</v>
+        <v>6811482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939283</v>
+        <v>125939238</v>
       </c>
       <c r="B21" t="n">
-        <v>78639</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,34 +2529,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454888</v>
+        <v>454804</v>
       </c>
       <c r="R21" t="n">
-        <v>6811478</v>
+        <v>6811564</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2578,7 +2583,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2589,6 +2594,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939285</v>
+        <v>125939246</v>
       </c>
       <c r="B22" t="n">
-        <v>77921</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454930</v>
+        <v>454944</v>
       </c>
       <c r="R22" t="n">
-        <v>6811482</v>
+        <v>6811441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939238</v>
+        <v>125939283</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>78639</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,39 +2733,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454804</v>
+        <v>454888</v>
       </c>
       <c r="R23" t="n">
-        <v>6811564</v>
+        <v>6811478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2777,7 +2782,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2788,11 +2793,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939264</v>
+        <v>125939229</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>79561</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454788</v>
+        <v>454945</v>
       </c>
       <c r="R45" t="n">
-        <v>6811599</v>
+        <v>6811496</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939219</v>
+        <v>125939264</v>
       </c>
       <c r="B46" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454849</v>
+        <v>454788</v>
       </c>
       <c r="R46" t="n">
-        <v>6811570</v>
+        <v>6811599</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939257</v>
+        <v>125939219</v>
       </c>
       <c r="B47" t="n">
-        <v>78730</v>
+        <v>79590</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454910</v>
+        <v>454849</v>
       </c>
       <c r="R47" t="n">
-        <v>6811442</v>
+        <v>6811570</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5152,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125939229</v>
+        <v>125939257</v>
       </c>
       <c r="B48" t="n">
-        <v>79561</v>
+        <v>78730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454945</v>
+        <v>454910</v>
       </c>
       <c r="R48" t="n">
-        <v>6811496</v>
+        <v>6811442</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R2" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R3" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939247</v>
+        <v>125939276</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>92524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454910</v>
+        <v>454947</v>
       </c>
       <c r="R4" t="n">
-        <v>6811441</v>
+        <v>6811454</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939282</v>
+        <v>125939247</v>
       </c>
       <c r="B5" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454870</v>
+        <v>454910</v>
       </c>
       <c r="R5" t="n">
-        <v>6811495</v>
+        <v>6811441</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939276</v>
+        <v>125939282</v>
       </c>
       <c r="B6" t="n">
-        <v>92522</v>
+        <v>78640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454947</v>
+        <v>454870</v>
       </c>
       <c r="R6" t="n">
-        <v>6811454</v>
+        <v>6811495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1163,7 +1163,7 @@
         <v>125939217</v>
       </c>
       <c r="B7" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125939256</v>
       </c>
       <c r="B8" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125939278</v>
       </c>
       <c r="B9" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125939286</v>
       </c>
       <c r="B10" t="n">
-        <v>78378</v>
+        <v>78379</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939223</v>
+        <v>125939277</v>
       </c>
       <c r="B11" t="n">
-        <v>79590</v>
+        <v>78640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454961</v>
+        <v>454907</v>
       </c>
       <c r="R11" t="n">
-        <v>6811450</v>
+        <v>6811355</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>125939250</v>
       </c>
       <c r="B12" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125939222</v>
       </c>
       <c r="B13" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>125939253</v>
       </c>
       <c r="B14" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939243</v>
+        <v>125939223</v>
       </c>
       <c r="B15" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454896</v>
+        <v>454961</v>
       </c>
       <c r="R15" t="n">
-        <v>6811477</v>
+        <v>6811450</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>125939230</v>
       </c>
       <c r="B16" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939277</v>
+        <v>125939243</v>
       </c>
       <c r="B17" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454907</v>
+        <v>454896</v>
       </c>
       <c r="R17" t="n">
-        <v>6811355</v>
+        <v>6811477</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B18" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R18" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>78640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R19" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939285</v>
+        <v>125939238</v>
       </c>
       <c r="B20" t="n">
-        <v>77921</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,34 +2432,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454930</v>
+        <v>454804</v>
       </c>
       <c r="R20" t="n">
-        <v>6811482</v>
+        <v>6811564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2481,7 +2486,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2492,6 +2497,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2518,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939238</v>
+        <v>125939283</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>78640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,39 +2539,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454804</v>
+        <v>454888</v>
       </c>
       <c r="R21" t="n">
-        <v>6811564</v>
+        <v>6811478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,7 +2588,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2594,11 +2599,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939246</v>
+        <v>125939285</v>
       </c>
       <c r="B22" t="n">
-        <v>78731</v>
+        <v>77922</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454944</v>
+        <v>454930</v>
       </c>
       <c r="R22" t="n">
-        <v>6811441</v>
+        <v>6811482</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939283</v>
+        <v>125939246</v>
       </c>
       <c r="B23" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454888</v>
+        <v>454944</v>
       </c>
       <c r="R23" t="n">
-        <v>6811478</v>
+        <v>6811441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2822,7 +2822,7 @@
         <v>125939262</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>125939263</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>125939233</v>
       </c>
       <c r="B26" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>125939242</v>
       </c>
       <c r="B27" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>125939273</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>125939269</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939281</v>
+        <v>125939231</v>
       </c>
       <c r="B30" t="n">
-        <v>78639</v>
+        <v>79068</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>967</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454865</v>
+        <v>454930</v>
       </c>
       <c r="R30" t="n">
-        <v>6811503</v>
+        <v>6811482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939270</v>
+        <v>125939281</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454944</v>
+        <v>454865</v>
       </c>
       <c r="R31" t="n">
-        <v>6811442</v>
+        <v>6811503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939231</v>
+        <v>125939270</v>
       </c>
       <c r="B32" t="n">
-        <v>79067</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454930</v>
+        <v>454944</v>
       </c>
       <c r="R32" t="n">
-        <v>6811482</v>
+        <v>6811442</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3700,7 +3700,7 @@
         <v>125939224</v>
       </c>
       <c r="B33" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>125939221</v>
       </c>
       <c r="B34" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>125939228</v>
       </c>
       <c r="B35" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>125939245</v>
       </c>
       <c r="B36" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939274</v>
+        <v>125939279</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454933</v>
+        <v>454802</v>
       </c>
       <c r="R37" t="n">
-        <v>6811343</v>
+        <v>6811557</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939265</v>
+        <v>125939218</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454793</v>
+        <v>454769</v>
       </c>
       <c r="R38" t="n">
-        <v>6811562</v>
+        <v>6811673</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939241</v>
+        <v>125939274</v>
       </c>
       <c r="B39" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454802</v>
+        <v>454933</v>
       </c>
       <c r="R39" t="n">
-        <v>6811558</v>
+        <v>6811343</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939279</v>
+        <v>125939265</v>
       </c>
       <c r="B40" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454802</v>
+        <v>454793</v>
       </c>
       <c r="R40" t="n">
-        <v>6811557</v>
+        <v>6811562</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939218</v>
+        <v>125939226</v>
       </c>
       <c r="B41" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454769</v>
+        <v>454938</v>
       </c>
       <c r="R41" t="n">
-        <v>6811673</v>
+        <v>6811337</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939226</v>
+        <v>125939241</v>
       </c>
       <c r="B42" t="n">
-        <v>79590</v>
+        <v>78732</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454938</v>
+        <v>454802</v>
       </c>
       <c r="R42" t="n">
-        <v>6811337</v>
+        <v>6811558</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4670,7 +4670,7 @@
         <v>125939266</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>125939227</v>
       </c>
       <c r="B44" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>125939229</v>
       </c>
       <c r="B45" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939264</v>
+        <v>125939219</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454788</v>
+        <v>454849</v>
       </c>
       <c r="R46" t="n">
-        <v>6811599</v>
+        <v>6811570</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939219</v>
+        <v>125939264</v>
       </c>
       <c r="B47" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454849</v>
+        <v>454788</v>
       </c>
       <c r="R47" t="n">
-        <v>6811570</v>
+        <v>6811599</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
         <v>125939257</v>
       </c>
       <c r="B48" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>125939284</v>
       </c>
       <c r="B49" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>125939225</v>
       </c>
       <c r="B50" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>125939267</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>125939260</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939268</v>
+        <v>125939251</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454882</v>
+        <v>454806</v>
       </c>
       <c r="R53" t="n">
-        <v>6811551</v>
+        <v>6811636</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5737,7 +5737,7 @@
         <v>125939271</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5831,10 +5831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939251</v>
+        <v>125939268</v>
       </c>
       <c r="B55" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5842,21 +5842,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454806</v>
+        <v>454882</v>
       </c>
       <c r="R55" t="n">
-        <v>6811636</v>
+        <v>6811551</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -5931,7 +5931,7 @@
         <v>125939248</v>
       </c>
       <c r="B56" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R2" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B3" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R3" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939250</v>
+        <v>125939230</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454931</v>
+        <v>454944</v>
       </c>
       <c r="R12" t="n">
-        <v>6811462</v>
+        <v>6811441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939222</v>
+        <v>125939250</v>
       </c>
       <c r="B13" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454945</v>
+        <v>454931</v>
       </c>
       <c r="R13" t="n">
-        <v>6811496</v>
+        <v>6811462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939253</v>
+        <v>125939222</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454880</v>
+        <v>454945</v>
       </c>
       <c r="R14" t="n">
-        <v>6811541</v>
+        <v>6811496</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939223</v>
+        <v>125939253</v>
       </c>
       <c r="B15" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454961</v>
+        <v>454880</v>
       </c>
       <c r="R15" t="n">
-        <v>6811450</v>
+        <v>6811541</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939230</v>
+        <v>125939223</v>
       </c>
       <c r="B16" t="n">
-        <v>79562</v>
+        <v>79591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454944</v>
+        <v>454961</v>
       </c>
       <c r="R16" t="n">
-        <v>6811441</v>
+        <v>6811450</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B18" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R18" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B19" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R19" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939238</v>
+        <v>125939283</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>78640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,39 +2432,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454804</v>
+        <v>454888</v>
       </c>
       <c r="R20" t="n">
-        <v>6811564</v>
+        <v>6811478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2486,7 +2481,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2497,11 +2492,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2528,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939283</v>
+        <v>125939246</v>
       </c>
       <c r="B21" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454888</v>
+        <v>454944</v>
       </c>
       <c r="R21" t="n">
-        <v>6811478</v>
+        <v>6811441</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2722,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939246</v>
+        <v>125939238</v>
       </c>
       <c r="B23" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,34 +2723,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454944</v>
+        <v>454804</v>
       </c>
       <c r="R23" t="n">
-        <v>6811441</v>
+        <v>6811564</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,7 +2777,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2793,6 +2788,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939231</v>
+        <v>125939281</v>
       </c>
       <c r="B30" t="n">
-        <v>79068</v>
+        <v>78640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>967</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454930</v>
+        <v>454865</v>
       </c>
       <c r="R30" t="n">
-        <v>6811482</v>
+        <v>6811503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939281</v>
+        <v>125939270</v>
       </c>
       <c r="B31" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454865</v>
+        <v>454944</v>
       </c>
       <c r="R31" t="n">
-        <v>6811503</v>
+        <v>6811442</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939270</v>
+        <v>125939224</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454944</v>
+        <v>454899</v>
       </c>
       <c r="R32" t="n">
-        <v>6811442</v>
+        <v>6811425</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939224</v>
+        <v>125939221</v>
       </c>
       <c r="B33" t="n">
         <v>79591</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454899</v>
+        <v>454868</v>
       </c>
       <c r="R33" t="n">
-        <v>6811425</v>
+        <v>6811496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939221</v>
+        <v>125939245</v>
       </c>
       <c r="B34" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454868</v>
+        <v>454945</v>
       </c>
       <c r="R34" t="n">
         <v>6811496</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939228</v>
+        <v>125939231</v>
       </c>
       <c r="B35" t="n">
-        <v>79562</v>
+        <v>79068</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454892</v>
+        <v>454930</v>
       </c>
       <c r="R35" t="n">
-        <v>6811478</v>
+        <v>6811482</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939245</v>
+        <v>125939228</v>
       </c>
       <c r="B36" t="n">
-        <v>78732</v>
+        <v>79562</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454945</v>
+        <v>454892</v>
       </c>
       <c r="R36" t="n">
-        <v>6811496</v>
+        <v>6811478</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -6023,6 +6023,109 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125939232</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91519</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>71</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>St. Skidbågåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>454788</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6811611</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Behöver mikroskoperas</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B2" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R2" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R3" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -872,7 +872,7 @@
         <v>125939276</v>
       </c>
       <c r="B4" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939278</v>
+        <v>125939286</v>
       </c>
       <c r="B9" t="n">
-        <v>78640</v>
+        <v>78379</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454854</v>
+        <v>454835</v>
       </c>
       <c r="R9" t="n">
-        <v>6811347</v>
+        <v>6811352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939286</v>
+        <v>125939278</v>
       </c>
       <c r="B10" t="n">
-        <v>78379</v>
+        <v>78640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454835</v>
+        <v>454854</v>
       </c>
       <c r="R10" t="n">
-        <v>6811352</v>
+        <v>6811347</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939277</v>
+        <v>125939230</v>
       </c>
       <c r="B11" t="n">
-        <v>78640</v>
+        <v>79562</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454907</v>
+        <v>454944</v>
       </c>
       <c r="R11" t="n">
-        <v>6811355</v>
+        <v>6811441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939230</v>
+        <v>125939243</v>
       </c>
       <c r="B12" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454944</v>
+        <v>454896</v>
       </c>
       <c r="R12" t="n">
-        <v>6811441</v>
+        <v>6811477</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939250</v>
+        <v>125939277</v>
       </c>
       <c r="B13" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454931</v>
+        <v>454907</v>
       </c>
       <c r="R13" t="n">
-        <v>6811462</v>
+        <v>6811355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939222</v>
+        <v>125939223</v>
       </c>
       <c r="B14" t="n">
         <v>79591</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454945</v>
+        <v>454961</v>
       </c>
       <c r="R14" t="n">
-        <v>6811496</v>
+        <v>6811450</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939253</v>
+        <v>125939250</v>
       </c>
       <c r="B15" t="n">
         <v>78731</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454880</v>
+        <v>454931</v>
       </c>
       <c r="R15" t="n">
-        <v>6811541</v>
+        <v>6811462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939223</v>
+        <v>125939222</v>
       </c>
       <c r="B16" t="n">
         <v>79591</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454961</v>
+        <v>454945</v>
       </c>
       <c r="R16" t="n">
-        <v>6811450</v>
+        <v>6811496</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939243</v>
+        <v>125939253</v>
       </c>
       <c r="B17" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454896</v>
+        <v>454880</v>
       </c>
       <c r="R17" t="n">
-        <v>6811477</v>
+        <v>6811541</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939283</v>
+        <v>125939285</v>
       </c>
       <c r="B20" t="n">
-        <v>78640</v>
+        <v>77922</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454888</v>
+        <v>454930</v>
       </c>
       <c r="R20" t="n">
-        <v>6811478</v>
+        <v>6811482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939246</v>
+        <v>125939238</v>
       </c>
       <c r="B21" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,34 +2529,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454944</v>
+        <v>454804</v>
       </c>
       <c r="R21" t="n">
-        <v>6811441</v>
+        <v>6811564</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2578,7 +2583,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2589,6 +2594,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939285</v>
+        <v>125939246</v>
       </c>
       <c r="B22" t="n">
-        <v>77922</v>
+        <v>78732</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454930</v>
+        <v>454944</v>
       </c>
       <c r="R22" t="n">
-        <v>6811482</v>
+        <v>6811441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939238</v>
+        <v>125939283</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>78640</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,39 +2733,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454804</v>
+        <v>454888</v>
       </c>
       <c r="R23" t="n">
-        <v>6811564</v>
+        <v>6811478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2777,7 +2782,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2788,11 +2793,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,7 +3212,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125939273</v>
+        <v>125939269</v>
       </c>
       <c r="B28" t="n">
         <v>78973</v>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454929</v>
+        <v>454964</v>
       </c>
       <c r="R28" t="n">
-        <v>6811379</v>
+        <v>6811440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125939269</v>
+        <v>125939273</v>
       </c>
       <c r="B29" t="n">
         <v>78973</v>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454964</v>
+        <v>454929</v>
       </c>
       <c r="R29" t="n">
-        <v>6811440</v>
+        <v>6811379</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939281</v>
+        <v>125939228</v>
       </c>
       <c r="B30" t="n">
-        <v>78640</v>
+        <v>79562</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454865</v>
+        <v>454892</v>
       </c>
       <c r="R30" t="n">
-        <v>6811503</v>
+        <v>6811478</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939270</v>
+        <v>125939245</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454944</v>
+        <v>454945</v>
       </c>
       <c r="R31" t="n">
-        <v>6811442</v>
+        <v>6811496</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939245</v>
+        <v>125939231</v>
       </c>
       <c r="B34" t="n">
-        <v>78732</v>
+        <v>79068</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454945</v>
+        <v>454930</v>
       </c>
       <c r="R34" t="n">
-        <v>6811496</v>
+        <v>6811482</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939231</v>
+        <v>125939281</v>
       </c>
       <c r="B35" t="n">
-        <v>79068</v>
+        <v>78640</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>967</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454930</v>
+        <v>454865</v>
       </c>
       <c r="R35" t="n">
-        <v>6811482</v>
+        <v>6811503</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939228</v>
+        <v>125939270</v>
       </c>
       <c r="B36" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454892</v>
+        <v>454944</v>
       </c>
       <c r="R36" t="n">
-        <v>6811478</v>
+        <v>6811442</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939279</v>
+        <v>125939274</v>
       </c>
       <c r="B37" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454802</v>
+        <v>454933</v>
       </c>
       <c r="R37" t="n">
-        <v>6811557</v>
+        <v>6811343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939218</v>
+        <v>125939265</v>
       </c>
       <c r="B38" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454769</v>
+        <v>454793</v>
       </c>
       <c r="R38" t="n">
-        <v>6811673</v>
+        <v>6811562</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939274</v>
+        <v>125939241</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454933</v>
+        <v>454802</v>
       </c>
       <c r="R39" t="n">
-        <v>6811343</v>
+        <v>6811558</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939265</v>
+        <v>125939279</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454793</v>
+        <v>454802</v>
       </c>
       <c r="R40" t="n">
-        <v>6811562</v>
+        <v>6811557</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939226</v>
+        <v>125939218</v>
       </c>
       <c r="B41" t="n">
         <v>79591</v>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454938</v>
+        <v>454769</v>
       </c>
       <c r="R41" t="n">
-        <v>6811337</v>
+        <v>6811673</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939241</v>
+        <v>125939226</v>
       </c>
       <c r="B42" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454802</v>
+        <v>454938</v>
       </c>
       <c r="R42" t="n">
-        <v>6811558</v>
+        <v>6811337</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939229</v>
+        <v>125939264</v>
       </c>
       <c r="B45" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454945</v>
+        <v>454788</v>
       </c>
       <c r="R45" t="n">
-        <v>6811496</v>
+        <v>6811599</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939264</v>
+        <v>125939257</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454788</v>
+        <v>454910</v>
       </c>
       <c r="R47" t="n">
-        <v>6811599</v>
+        <v>6811442</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5152,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125939257</v>
+        <v>125939229</v>
       </c>
       <c r="B48" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454910</v>
+        <v>454945</v>
       </c>
       <c r="R48" t="n">
-        <v>6811442</v>
+        <v>6811496</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B49" t="n">
-        <v>78640</v>
+        <v>79591</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R49" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B50" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R50" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939260</v>
+        <v>125939251</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454706</v>
+        <v>454806</v>
       </c>
       <c r="R52" t="n">
-        <v>6811484</v>
+        <v>6811636</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939251</v>
+        <v>125939268</v>
       </c>
       <c r="B53" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454806</v>
+        <v>454882</v>
       </c>
       <c r="R53" t="n">
-        <v>6811636</v>
+        <v>6811551</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5734,7 +5734,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939271</v>
+        <v>125939260</v>
       </c>
       <c r="B54" t="n">
         <v>78973</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454943</v>
+        <v>454706</v>
       </c>
       <c r="R54" t="n">
-        <v>6811446</v>
+        <v>6811484</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5831,7 +5831,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939268</v>
+        <v>125939271</v>
       </c>
       <c r="B55" t="n">
         <v>78973</v>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454882</v>
+        <v>454943</v>
       </c>
       <c r="R55" t="n">
-        <v>6811551</v>
+        <v>6811446</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
         <v>125939232</v>
       </c>
       <c r="B57" t="n">
-        <v>91519</v>
+        <v>91521</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R2" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B3" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R3" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B4" t="n">
-        <v>92526</v>
+        <v>78732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R4" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939247</v>
+        <v>125939282</v>
       </c>
       <c r="B5" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454910</v>
+        <v>454870</v>
       </c>
       <c r="R5" t="n">
-        <v>6811441</v>
+        <v>6811495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939282</v>
+        <v>125939276</v>
       </c>
       <c r="B6" t="n">
-        <v>78640</v>
+        <v>92526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454870</v>
+        <v>454947</v>
       </c>
       <c r="R6" t="n">
-        <v>6811495</v>
+        <v>6811454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939286</v>
+        <v>125939278</v>
       </c>
       <c r="B9" t="n">
-        <v>78379</v>
+        <v>78640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454835</v>
+        <v>454854</v>
       </c>
       <c r="R9" t="n">
-        <v>6811352</v>
+        <v>6811347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939278</v>
+        <v>125939286</v>
       </c>
       <c r="B10" t="n">
-        <v>78640</v>
+        <v>78379</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454854</v>
+        <v>454835</v>
       </c>
       <c r="R10" t="n">
-        <v>6811347</v>
+        <v>6811352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939285</v>
+        <v>125939283</v>
       </c>
       <c r="B20" t="n">
-        <v>77922</v>
+        <v>78640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454930</v>
+        <v>454888</v>
       </c>
       <c r="R20" t="n">
-        <v>6811482</v>
+        <v>6811478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939238</v>
+        <v>125939285</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>77922</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,39 +2529,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454804</v>
+        <v>454930</v>
       </c>
       <c r="R21" t="n">
-        <v>6811564</v>
+        <v>6811482</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,7 +2578,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2594,11 +2589,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2625,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939246</v>
+        <v>125939238</v>
       </c>
       <c r="B22" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,34 +2626,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454944</v>
+        <v>454804</v>
       </c>
       <c r="R22" t="n">
-        <v>6811441</v>
+        <v>6811564</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,7 +2680,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2696,6 +2691,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939283</v>
+        <v>125939246</v>
       </c>
       <c r="B23" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454888</v>
+        <v>454944</v>
       </c>
       <c r="R23" t="n">
-        <v>6811478</v>
+        <v>6811441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939274</v>
+        <v>125939241</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454933</v>
+        <v>454802</v>
       </c>
       <c r="R37" t="n">
-        <v>6811343</v>
+        <v>6811558</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939265</v>
+        <v>125939279</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454793</v>
+        <v>454802</v>
       </c>
       <c r="R38" t="n">
-        <v>6811562</v>
+        <v>6811557</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939241</v>
+        <v>125939274</v>
       </c>
       <c r="B39" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454802</v>
+        <v>454933</v>
       </c>
       <c r="R39" t="n">
-        <v>6811558</v>
+        <v>6811343</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939279</v>
+        <v>125939265</v>
       </c>
       <c r="B40" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454802</v>
+        <v>454793</v>
       </c>
       <c r="R40" t="n">
-        <v>6811557</v>
+        <v>6811562</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939247</v>
+        <v>125939276</v>
       </c>
       <c r="B4" t="n">
-        <v>78732</v>
+        <v>92528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454910</v>
+        <v>454947</v>
       </c>
       <c r="R4" t="n">
-        <v>6811441</v>
+        <v>6811454</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B6" t="n">
-        <v>92526</v>
+        <v>78732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R6" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125939217</v>
+        <v>125939256</v>
       </c>
       <c r="B7" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454837</v>
+        <v>454960</v>
       </c>
       <c r="R7" t="n">
-        <v>6811351</v>
+        <v>6811451</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939256</v>
+        <v>125939217</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454960</v>
+        <v>454837</v>
       </c>
       <c r="R8" t="n">
-        <v>6811451</v>
+        <v>6811351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939278</v>
+        <v>125939286</v>
       </c>
       <c r="B9" t="n">
-        <v>78640</v>
+        <v>78379</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454854</v>
+        <v>454835</v>
       </c>
       <c r="R9" t="n">
-        <v>6811347</v>
+        <v>6811352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939286</v>
+        <v>125939278</v>
       </c>
       <c r="B10" t="n">
-        <v>78379</v>
+        <v>78640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454835</v>
+        <v>454854</v>
       </c>
       <c r="R10" t="n">
-        <v>6811352</v>
+        <v>6811347</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939230</v>
+        <v>125939243</v>
       </c>
       <c r="B11" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454944</v>
+        <v>454896</v>
       </c>
       <c r="R11" t="n">
-        <v>6811441</v>
+        <v>6811477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939243</v>
+        <v>125939250</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454896</v>
+        <v>454931</v>
       </c>
       <c r="R12" t="n">
-        <v>6811477</v>
+        <v>6811462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939277</v>
+        <v>125939253</v>
       </c>
       <c r="B13" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454907</v>
+        <v>454880</v>
       </c>
       <c r="R13" t="n">
-        <v>6811355</v>
+        <v>6811541</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939250</v>
+        <v>125939277</v>
       </c>
       <c r="B15" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454931</v>
+        <v>454907</v>
       </c>
       <c r="R15" t="n">
-        <v>6811462</v>
+        <v>6811355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939253</v>
+        <v>125939230</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454880</v>
+        <v>454944</v>
       </c>
       <c r="R17" t="n">
-        <v>6811541</v>
+        <v>6811441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B18" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R18" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B19" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R19" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939283</v>
+        <v>125939246</v>
       </c>
       <c r="B20" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454888</v>
+        <v>454944</v>
       </c>
       <c r="R20" t="n">
-        <v>6811478</v>
+        <v>6811441</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939285</v>
+        <v>125939283</v>
       </c>
       <c r="B21" t="n">
-        <v>77922</v>
+        <v>78640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454930</v>
+        <v>454888</v>
       </c>
       <c r="R21" t="n">
-        <v>6811482</v>
+        <v>6811478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939238</v>
+        <v>125939285</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>77922</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,39 +2626,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454804</v>
+        <v>454930</v>
       </c>
       <c r="R22" t="n">
-        <v>6811564</v>
+        <v>6811482</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,7 +2675,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2691,11 +2686,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939246</v>
+        <v>125939238</v>
       </c>
       <c r="B23" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,34 +2723,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454944</v>
+        <v>454804</v>
       </c>
       <c r="R23" t="n">
-        <v>6811441</v>
+        <v>6811564</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,7 +2777,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2793,6 +2788,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2819,7 +2819,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939262</v>
+        <v>125939263</v>
       </c>
       <c r="B24" t="n">
         <v>78973</v>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454710</v>
+        <v>454734</v>
       </c>
       <c r="R24" t="n">
-        <v>6811492</v>
+        <v>6811565</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125939263</v>
+        <v>125939262</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454734</v>
+        <v>454710</v>
       </c>
       <c r="R25" t="n">
-        <v>6811565</v>
+        <v>6811492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3212,7 +3212,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125939269</v>
+        <v>125939273</v>
       </c>
       <c r="B28" t="n">
         <v>78973</v>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454964</v>
+        <v>454929</v>
       </c>
       <c r="R28" t="n">
-        <v>6811440</v>
+        <v>6811379</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125939273</v>
+        <v>125939269</v>
       </c>
       <c r="B29" t="n">
         <v>78973</v>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454929</v>
+        <v>454964</v>
       </c>
       <c r="R29" t="n">
-        <v>6811379</v>
+        <v>6811440</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939228</v>
+        <v>125939221</v>
       </c>
       <c r="B30" t="n">
-        <v>79562</v>
+        <v>79591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454892</v>
+        <v>454868</v>
       </c>
       <c r="R30" t="n">
-        <v>6811478</v>
+        <v>6811496</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939245</v>
+        <v>125939270</v>
       </c>
       <c r="B31" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454945</v>
+        <v>454944</v>
       </c>
       <c r="R31" t="n">
-        <v>6811496</v>
+        <v>6811442</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939221</v>
+        <v>125939231</v>
       </c>
       <c r="B33" t="n">
-        <v>79591</v>
+        <v>79068</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454868</v>
+        <v>454930</v>
       </c>
       <c r="R33" t="n">
-        <v>6811496</v>
+        <v>6811482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939231</v>
+        <v>125939281</v>
       </c>
       <c r="B34" t="n">
-        <v>79068</v>
+        <v>78640</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>967</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454930</v>
+        <v>454865</v>
       </c>
       <c r="R34" t="n">
-        <v>6811482</v>
+        <v>6811503</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939281</v>
+        <v>125939245</v>
       </c>
       <c r="B35" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454865</v>
+        <v>454945</v>
       </c>
       <c r="R35" t="n">
-        <v>6811503</v>
+        <v>6811496</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939270</v>
+        <v>125939228</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454944</v>
+        <v>454892</v>
       </c>
       <c r="R36" t="n">
-        <v>6811442</v>
+        <v>6811478</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939241</v>
+        <v>125939218</v>
       </c>
       <c r="B37" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454802</v>
+        <v>454769</v>
       </c>
       <c r="R37" t="n">
-        <v>6811558</v>
+        <v>6811673</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939279</v>
+        <v>125939241</v>
       </c>
       <c r="B38" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4220,7 +4220,7 @@
         <v>454802</v>
       </c>
       <c r="R38" t="n">
-        <v>6811557</v>
+        <v>6811558</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939265</v>
+        <v>125939226</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454793</v>
+        <v>454938</v>
       </c>
       <c r="R40" t="n">
-        <v>6811562</v>
+        <v>6811337</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939218</v>
+        <v>125939265</v>
       </c>
       <c r="B41" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454769</v>
+        <v>454793</v>
       </c>
       <c r="R41" t="n">
-        <v>6811673</v>
+        <v>6811562</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939226</v>
+        <v>125939279</v>
       </c>
       <c r="B42" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454938</v>
+        <v>454802</v>
       </c>
       <c r="R42" t="n">
-        <v>6811337</v>
+        <v>6811557</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939219</v>
+        <v>125939257</v>
       </c>
       <c r="B46" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454849</v>
+        <v>454910</v>
       </c>
       <c r="R46" t="n">
-        <v>6811570</v>
+        <v>6811442</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939257</v>
+        <v>125939219</v>
       </c>
       <c r="B47" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454910</v>
+        <v>454849</v>
       </c>
       <c r="R47" t="n">
-        <v>6811442</v>
+        <v>6811570</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B49" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R49" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B50" t="n">
-        <v>78640</v>
+        <v>79591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R50" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939251</v>
+        <v>125939248</v>
       </c>
       <c r="B52" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454806</v>
+        <v>454938</v>
       </c>
       <c r="R52" t="n">
-        <v>6811636</v>
+        <v>6811339</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5637,7 +5637,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939268</v>
+        <v>125939260</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454882</v>
+        <v>454706</v>
       </c>
       <c r="R53" t="n">
-        <v>6811551</v>
+        <v>6811484</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5734,7 +5734,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939260</v>
+        <v>125939268</v>
       </c>
       <c r="B54" t="n">
         <v>78973</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454706</v>
+        <v>454882</v>
       </c>
       <c r="R54" t="n">
-        <v>6811484</v>
+        <v>6811551</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5831,10 +5831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939271</v>
+        <v>125939251</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5842,21 +5842,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454943</v>
+        <v>454806</v>
       </c>
       <c r="R55" t="n">
-        <v>6811446</v>
+        <v>6811636</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -5928,10 +5928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939248</v>
+        <v>125939271</v>
       </c>
       <c r="B56" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454938</v>
+        <v>454943</v>
       </c>
       <c r="R56" t="n">
-        <v>6811339</v>
+        <v>6811446</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
         <v>125939232</v>
       </c>
       <c r="B57" t="n">
-        <v>91521</v>
+        <v>91523</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B18" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R18" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B19" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R19" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939263</v>
+        <v>125939242</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454734</v>
+        <v>454883</v>
       </c>
       <c r="R24" t="n">
-        <v>6811565</v>
+        <v>6811548</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125939262</v>
+        <v>125939263</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454710</v>
+        <v>454734</v>
       </c>
       <c r="R25" t="n">
-        <v>6811492</v>
+        <v>6811565</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,50 +3013,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939233</v>
+        <v>125939262</v>
       </c>
       <c r="B26" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454794</v>
+        <v>454710</v>
       </c>
       <c r="R26" t="n">
-        <v>6811612</v>
+        <v>6811492</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3115,45 +3110,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125939242</v>
+        <v>125939233</v>
       </c>
       <c r="B27" t="n">
-        <v>78732</v>
+        <v>56844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454883</v>
+        <v>454794</v>
       </c>
       <c r="R27" t="n">
-        <v>6811548</v>
+        <v>6811612</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939221</v>
+        <v>125939231</v>
       </c>
       <c r="B30" t="n">
-        <v>79591</v>
+        <v>79068</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454868</v>
+        <v>454930</v>
       </c>
       <c r="R30" t="n">
-        <v>6811496</v>
+        <v>6811482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939270</v>
+        <v>125939281</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454944</v>
+        <v>454865</v>
       </c>
       <c r="R31" t="n">
-        <v>6811442</v>
+        <v>6811503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939224</v>
+        <v>125939270</v>
       </c>
       <c r="B32" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454899</v>
+        <v>454944</v>
       </c>
       <c r="R32" t="n">
-        <v>6811425</v>
+        <v>6811442</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939231</v>
+        <v>125939224</v>
       </c>
       <c r="B33" t="n">
-        <v>79068</v>
+        <v>79591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454930</v>
+        <v>454899</v>
       </c>
       <c r="R33" t="n">
-        <v>6811482</v>
+        <v>6811425</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939281</v>
+        <v>125939221</v>
       </c>
       <c r="B34" t="n">
-        <v>78640</v>
+        <v>79591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454865</v>
+        <v>454868</v>
       </c>
       <c r="R34" t="n">
-        <v>6811503</v>
+        <v>6811496</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939218</v>
+        <v>125939274</v>
       </c>
       <c r="B37" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454769</v>
+        <v>454933</v>
       </c>
       <c r="R37" t="n">
-        <v>6811673</v>
+        <v>6811343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939241</v>
+        <v>125939226</v>
       </c>
       <c r="B38" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454802</v>
+        <v>454938</v>
       </c>
       <c r="R38" t="n">
-        <v>6811558</v>
+        <v>6811337</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939274</v>
+        <v>125939265</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454933</v>
+        <v>454793</v>
       </c>
       <c r="R39" t="n">
-        <v>6811343</v>
+        <v>6811562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939226</v>
+        <v>125939279</v>
       </c>
       <c r="B40" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454938</v>
+        <v>454802</v>
       </c>
       <c r="R40" t="n">
-        <v>6811337</v>
+        <v>6811557</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939265</v>
+        <v>125939218</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454793</v>
+        <v>454769</v>
       </c>
       <c r="R41" t="n">
-        <v>6811562</v>
+        <v>6811673</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939279</v>
+        <v>125939241</v>
       </c>
       <c r="B42" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4608,7 +4608,7 @@
         <v>454802</v>
       </c>
       <c r="R42" t="n">
-        <v>6811557</v>
+        <v>6811558</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939264</v>
+        <v>125939219</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454788</v>
+        <v>454849</v>
       </c>
       <c r="R45" t="n">
-        <v>6811599</v>
+        <v>6811570</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939257</v>
+        <v>125939264</v>
       </c>
       <c r="B46" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454910</v>
+        <v>454788</v>
       </c>
       <c r="R46" t="n">
-        <v>6811442</v>
+        <v>6811599</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939219</v>
+        <v>125939257</v>
       </c>
       <c r="B47" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454849</v>
+        <v>454910</v>
       </c>
       <c r="R47" t="n">
-        <v>6811570</v>
+        <v>6811442</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939248</v>
+        <v>125939260</v>
       </c>
       <c r="B52" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454938</v>
+        <v>454706</v>
       </c>
       <c r="R52" t="n">
-        <v>6811339</v>
+        <v>6811484</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5637,7 +5637,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939260</v>
+        <v>125939268</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454706</v>
+        <v>454882</v>
       </c>
       <c r="R53" t="n">
-        <v>6811484</v>
+        <v>6811551</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5734,10 +5734,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939268</v>
+        <v>125939251</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5745,21 +5745,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454882</v>
+        <v>454806</v>
       </c>
       <c r="R54" t="n">
-        <v>6811551</v>
+        <v>6811636</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5831,10 +5831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939251</v>
+        <v>125939271</v>
       </c>
       <c r="B55" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5842,21 +5842,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454806</v>
+        <v>454943</v>
       </c>
       <c r="R55" t="n">
-        <v>6811636</v>
+        <v>6811446</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -5928,10 +5928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939271</v>
+        <v>125939248</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454943</v>
+        <v>454938</v>
       </c>
       <c r="R56" t="n">
-        <v>6811446</v>
+        <v>6811339</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B2" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R2" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R3" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B4" t="n">
-        <v>92528</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R4" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939282</v>
+        <v>125939276</v>
       </c>
       <c r="B5" t="n">
-        <v>78640</v>
+        <v>92532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454870</v>
+        <v>454947</v>
       </c>
       <c r="R5" t="n">
-        <v>6811495</v>
+        <v>6811454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939247</v>
+        <v>125939282</v>
       </c>
       <c r="B6" t="n">
-        <v>78732</v>
+        <v>78644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454910</v>
+        <v>454870</v>
       </c>
       <c r="R6" t="n">
-        <v>6811441</v>
+        <v>6811495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125939256</v>
+        <v>125939217</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>79595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454960</v>
+        <v>454837</v>
       </c>
       <c r="R7" t="n">
-        <v>6811451</v>
+        <v>6811351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939217</v>
+        <v>125939256</v>
       </c>
       <c r="B8" t="n">
-        <v>79591</v>
+        <v>78735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454837</v>
+        <v>454960</v>
       </c>
       <c r="R8" t="n">
-        <v>6811351</v>
+        <v>6811451</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1357,7 +1357,7 @@
         <v>125939286</v>
       </c>
       <c r="B9" t="n">
-        <v>78379</v>
+        <v>78383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125939278</v>
       </c>
       <c r="B10" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939243</v>
+        <v>125939223</v>
       </c>
       <c r="B11" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454896</v>
+        <v>454961</v>
       </c>
       <c r="R11" t="n">
-        <v>6811477</v>
+        <v>6811450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>125939250</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939253</v>
+        <v>125939222</v>
       </c>
       <c r="B13" t="n">
-        <v>78731</v>
+        <v>79595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454880</v>
+        <v>454945</v>
       </c>
       <c r="R13" t="n">
-        <v>6811541</v>
+        <v>6811496</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939223</v>
+        <v>125939253</v>
       </c>
       <c r="B14" t="n">
-        <v>79591</v>
+        <v>78735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454961</v>
+        <v>454880</v>
       </c>
       <c r="R14" t="n">
-        <v>6811450</v>
+        <v>6811541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
         <v>125939277</v>
       </c>
       <c r="B15" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939222</v>
+        <v>125939243</v>
       </c>
       <c r="B16" t="n">
-        <v>79591</v>
+        <v>78736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454945</v>
+        <v>454896</v>
       </c>
       <c r="R16" t="n">
-        <v>6811496</v>
+        <v>6811477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>125939230</v>
       </c>
       <c r="B17" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B18" t="n">
-        <v>78640</v>
+        <v>78735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R18" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B19" t="n">
-        <v>78731</v>
+        <v>78644</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R19" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939246</v>
+        <v>125939285</v>
       </c>
       <c r="B20" t="n">
-        <v>78732</v>
+        <v>77926</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454944</v>
+        <v>454930</v>
       </c>
       <c r="R20" t="n">
-        <v>6811441</v>
+        <v>6811482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
         <v>125939283</v>
       </c>
       <c r="B21" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939285</v>
+        <v>125939238</v>
       </c>
       <c r="B22" t="n">
-        <v>77922</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,34 +2626,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454930</v>
+        <v>454804</v>
       </c>
       <c r="R22" t="n">
-        <v>6811482</v>
+        <v>6811564</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2675,7 +2680,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2686,6 +2691,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2712,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939238</v>
+        <v>125939246</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>78736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,39 +2733,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454804</v>
+        <v>454944</v>
       </c>
       <c r="R23" t="n">
-        <v>6811564</v>
+        <v>6811441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2777,7 +2782,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2788,11 +2793,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939242</v>
+        <v>125939262</v>
       </c>
       <c r="B24" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454883</v>
+        <v>454710</v>
       </c>
       <c r="R24" t="n">
-        <v>6811548</v>
+        <v>6811492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2919,7 +2919,7 @@
         <v>125939263</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3013,45 +3013,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939262</v>
+        <v>125939233</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>56848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454710</v>
+        <v>454794</v>
       </c>
       <c r="R26" t="n">
-        <v>6811492</v>
+        <v>6811612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,50 +3115,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125939233</v>
+        <v>125939242</v>
       </c>
       <c r="B27" t="n">
-        <v>56844</v>
+        <v>78736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454794</v>
+        <v>454883</v>
       </c>
       <c r="R27" t="n">
-        <v>6811612</v>
+        <v>6811548</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3215,7 +3215,7 @@
         <v>125939273</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>125939269</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939231</v>
+        <v>125939281</v>
       </c>
       <c r="B30" t="n">
-        <v>79068</v>
+        <v>78644</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>967</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454930</v>
+        <v>454865</v>
       </c>
       <c r="R30" t="n">
-        <v>6811482</v>
+        <v>6811503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939281</v>
+        <v>125939231</v>
       </c>
       <c r="B31" t="n">
-        <v>78640</v>
+        <v>79072</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>967</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454865</v>
+        <v>454930</v>
       </c>
       <c r="R31" t="n">
-        <v>6811503</v>
+        <v>6811482</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3603,7 +3603,7 @@
         <v>125939270</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>125939224</v>
       </c>
       <c r="B33" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>125939221</v>
       </c>
       <c r="B34" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939245</v>
+        <v>125939228</v>
       </c>
       <c r="B35" t="n">
-        <v>78732</v>
+        <v>79566</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454945</v>
+        <v>454892</v>
       </c>
       <c r="R35" t="n">
-        <v>6811496</v>
+        <v>6811478</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939228</v>
+        <v>125939245</v>
       </c>
       <c r="B36" t="n">
-        <v>79562</v>
+        <v>78736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454892</v>
+        <v>454945</v>
       </c>
       <c r="R36" t="n">
-        <v>6811478</v>
+        <v>6811496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939274</v>
+        <v>125939218</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454933</v>
+        <v>454769</v>
       </c>
       <c r="R37" t="n">
-        <v>6811343</v>
+        <v>6811673</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939226</v>
+        <v>125939274</v>
       </c>
       <c r="B38" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454938</v>
+        <v>454933</v>
       </c>
       <c r="R38" t="n">
-        <v>6811337</v>
+        <v>6811343</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4282,7 +4282,7 @@
         <v>125939265</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939279</v>
+        <v>125939226</v>
       </c>
       <c r="B40" t="n">
-        <v>78640</v>
+        <v>79595</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454802</v>
+        <v>454938</v>
       </c>
       <c r="R40" t="n">
-        <v>6811557</v>
+        <v>6811337</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939218</v>
+        <v>125939279</v>
       </c>
       <c r="B41" t="n">
-        <v>79591</v>
+        <v>78644</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454769</v>
+        <v>454802</v>
       </c>
       <c r="R41" t="n">
-        <v>6811673</v>
+        <v>6811557</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4573,7 +4573,7 @@
         <v>125939241</v>
       </c>
       <c r="B42" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>125939266</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>125939227</v>
       </c>
       <c r="B44" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939219</v>
+        <v>125939229</v>
       </c>
       <c r="B45" t="n">
-        <v>79591</v>
+        <v>79566</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454849</v>
+        <v>454945</v>
       </c>
       <c r="R45" t="n">
-        <v>6811570</v>
+        <v>6811496</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939264</v>
+        <v>125939219</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454788</v>
+        <v>454849</v>
       </c>
       <c r="R46" t="n">
-        <v>6811599</v>
+        <v>6811570</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939257</v>
+        <v>125939264</v>
       </c>
       <c r="B47" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454910</v>
+        <v>454788</v>
       </c>
       <c r="R47" t="n">
-        <v>6811442</v>
+        <v>6811599</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5152,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125939229</v>
+        <v>125939257</v>
       </c>
       <c r="B48" t="n">
-        <v>79562</v>
+        <v>78735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454945</v>
+        <v>454910</v>
       </c>
       <c r="R48" t="n">
-        <v>6811496</v>
+        <v>6811442</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B49" t="n">
-        <v>78640</v>
+        <v>79595</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R49" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B50" t="n">
-        <v>79591</v>
+        <v>78644</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R50" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5446,7 +5446,7 @@
         <v>125939267</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>125939260</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939268</v>
+        <v>125939251</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>78735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454882</v>
+        <v>454806</v>
       </c>
       <c r="R53" t="n">
-        <v>6811551</v>
+        <v>6811636</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5734,10 +5734,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939251</v>
+        <v>125939271</v>
       </c>
       <c r="B54" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5745,21 +5745,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454806</v>
+        <v>454943</v>
       </c>
       <c r="R54" t="n">
-        <v>6811636</v>
+        <v>6811446</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5831,10 +5831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939271</v>
+        <v>125939268</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454943</v>
+        <v>454882</v>
       </c>
       <c r="R55" t="n">
-        <v>6811446</v>
+        <v>6811551</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,7 +5931,7 @@
         <v>125939248</v>
       </c>
       <c r="B56" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>125939232</v>
       </c>
       <c r="B57" t="n">
-        <v>91523</v>
+        <v>91527</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R2" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R3" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939223</v>
+        <v>125939243</v>
       </c>
       <c r="B11" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454961</v>
+        <v>454896</v>
       </c>
       <c r="R11" t="n">
-        <v>6811450</v>
+        <v>6811477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939250</v>
+        <v>125939230</v>
       </c>
       <c r="B12" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454931</v>
+        <v>454944</v>
       </c>
       <c r="R12" t="n">
-        <v>6811462</v>
+        <v>6811441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939222</v>
+        <v>125939223</v>
       </c>
       <c r="B13" t="n">
         <v>79595</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454945</v>
+        <v>454961</v>
       </c>
       <c r="R13" t="n">
-        <v>6811496</v>
+        <v>6811450</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939253</v>
+        <v>125939250</v>
       </c>
       <c r="B14" t="n">
         <v>78735</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454880</v>
+        <v>454931</v>
       </c>
       <c r="R14" t="n">
-        <v>6811541</v>
+        <v>6811462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939277</v>
+        <v>125939222</v>
       </c>
       <c r="B15" t="n">
-        <v>78644</v>
+        <v>79595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454907</v>
+        <v>454945</v>
       </c>
       <c r="R15" t="n">
-        <v>6811355</v>
+        <v>6811496</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939243</v>
+        <v>125939253</v>
       </c>
       <c r="B16" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454896</v>
+        <v>454880</v>
       </c>
       <c r="R16" t="n">
-        <v>6811477</v>
+        <v>6811541</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939230</v>
+        <v>125939277</v>
       </c>
       <c r="B17" t="n">
-        <v>79566</v>
+        <v>78644</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454944</v>
+        <v>454907</v>
       </c>
       <c r="R17" t="n">
-        <v>6811441</v>
+        <v>6811355</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939281</v>
+        <v>125939270</v>
       </c>
       <c r="B30" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454865</v>
+        <v>454944</v>
       </c>
       <c r="R30" t="n">
-        <v>6811503</v>
+        <v>6811442</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939231</v>
+        <v>125939224</v>
       </c>
       <c r="B31" t="n">
-        <v>79072</v>
+        <v>79595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454930</v>
+        <v>454899</v>
       </c>
       <c r="R31" t="n">
-        <v>6811482</v>
+        <v>6811425</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939270</v>
+        <v>125939221</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454944</v>
+        <v>454868</v>
       </c>
       <c r="R32" t="n">
-        <v>6811442</v>
+        <v>6811496</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939224</v>
+        <v>125939281</v>
       </c>
       <c r="B33" t="n">
-        <v>79595</v>
+        <v>78644</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454899</v>
+        <v>454865</v>
       </c>
       <c r="R33" t="n">
-        <v>6811425</v>
+        <v>6811503</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939221</v>
+        <v>125939231</v>
       </c>
       <c r="B34" t="n">
-        <v>79595</v>
+        <v>79072</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454868</v>
+        <v>454930</v>
       </c>
       <c r="R34" t="n">
-        <v>6811496</v>
+        <v>6811482</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939228</v>
+        <v>125939245</v>
       </c>
       <c r="B35" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454892</v>
+        <v>454945</v>
       </c>
       <c r="R35" t="n">
-        <v>6811478</v>
+        <v>6811496</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939245</v>
+        <v>125939228</v>
       </c>
       <c r="B36" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454945</v>
+        <v>454892</v>
       </c>
       <c r="R36" t="n">
-        <v>6811496</v>
+        <v>6811478</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939247</v>
+        <v>125939282</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454910</v>
+        <v>454870</v>
       </c>
       <c r="R4" t="n">
-        <v>6811441</v>
+        <v>6811495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -929,7 +929,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939282</v>
+        <v>125939247</v>
       </c>
       <c r="B6" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454870</v>
+        <v>454910</v>
       </c>
       <c r="R6" t="n">
-        <v>6811495</v>
+        <v>6811441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939223</v>
+        <v>125939277</v>
       </c>
       <c r="B13" t="n">
-        <v>79595</v>
+        <v>78644</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454961</v>
+        <v>454907</v>
       </c>
       <c r="R13" t="n">
-        <v>6811450</v>
+        <v>6811355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939250</v>
+        <v>125939223</v>
       </c>
       <c r="B14" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454931</v>
+        <v>454961</v>
       </c>
       <c r="R14" t="n">
-        <v>6811462</v>
+        <v>6811450</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939222</v>
+        <v>125939250</v>
       </c>
       <c r="B15" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454945</v>
+        <v>454931</v>
       </c>
       <c r="R15" t="n">
-        <v>6811496</v>
+        <v>6811462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939253</v>
+        <v>125939222</v>
       </c>
       <c r="B16" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454880</v>
+        <v>454945</v>
       </c>
       <c r="R16" t="n">
-        <v>6811541</v>
+        <v>6811496</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939277</v>
+        <v>125939253</v>
       </c>
       <c r="B17" t="n">
-        <v>78644</v>
+        <v>78735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454907</v>
+        <v>454880</v>
       </c>
       <c r="R17" t="n">
-        <v>6811355</v>
+        <v>6811541</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B18" t="n">
-        <v>78735</v>
+        <v>78644</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R18" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B19" t="n">
-        <v>78644</v>
+        <v>78735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R19" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939283</v>
+        <v>125939238</v>
       </c>
       <c r="B21" t="n">
-        <v>78644</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,34 +2529,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454888</v>
+        <v>454804</v>
       </c>
       <c r="R21" t="n">
-        <v>6811478</v>
+        <v>6811564</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2578,7 +2583,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2589,6 +2594,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939238</v>
+        <v>125939283</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>78644</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,39 +2636,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454804</v>
+        <v>454888</v>
       </c>
       <c r="R22" t="n">
-        <v>6811564</v>
+        <v>6811478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,7 +2685,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2691,11 +2696,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939270</v>
+        <v>125939231</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>79072</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454944</v>
+        <v>454930</v>
       </c>
       <c r="R30" t="n">
-        <v>6811442</v>
+        <v>6811482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939224</v>
+        <v>125939281</v>
       </c>
       <c r="B31" t="n">
-        <v>79595</v>
+        <v>78644</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454899</v>
+        <v>454865</v>
       </c>
       <c r="R31" t="n">
-        <v>6811425</v>
+        <v>6811503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939221</v>
+        <v>125939270</v>
       </c>
       <c r="B32" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454868</v>
+        <v>454944</v>
       </c>
       <c r="R32" t="n">
-        <v>6811496</v>
+        <v>6811442</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939281</v>
+        <v>125939224</v>
       </c>
       <c r="B33" t="n">
-        <v>78644</v>
+        <v>79595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454865</v>
+        <v>454899</v>
       </c>
       <c r="R33" t="n">
-        <v>6811503</v>
+        <v>6811425</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939231</v>
+        <v>125939221</v>
       </c>
       <c r="B34" t="n">
-        <v>79072</v>
+        <v>79595</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454930</v>
+        <v>454868</v>
       </c>
       <c r="R34" t="n">
-        <v>6811482</v>
+        <v>6811496</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939245</v>
+        <v>125939228</v>
       </c>
       <c r="B35" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454945</v>
+        <v>454892</v>
       </c>
       <c r="R35" t="n">
-        <v>6811496</v>
+        <v>6811478</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939228</v>
+        <v>125939245</v>
       </c>
       <c r="B36" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454892</v>
+        <v>454945</v>
       </c>
       <c r="R36" t="n">
-        <v>6811478</v>
+        <v>6811496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939218</v>
+        <v>125939279</v>
       </c>
       <c r="B37" t="n">
-        <v>79595</v>
+        <v>78644</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454769</v>
+        <v>454802</v>
       </c>
       <c r="R37" t="n">
-        <v>6811673</v>
+        <v>6811557</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939274</v>
+        <v>125939218</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454933</v>
+        <v>454769</v>
       </c>
       <c r="R38" t="n">
-        <v>6811343</v>
+        <v>6811673</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939265</v>
+        <v>125939274</v>
       </c>
       <c r="B39" t="n">
         <v>78977</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454793</v>
+        <v>454933</v>
       </c>
       <c r="R39" t="n">
-        <v>6811562</v>
+        <v>6811343</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939226</v>
+        <v>125939265</v>
       </c>
       <c r="B40" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454938</v>
+        <v>454793</v>
       </c>
       <c r="R40" t="n">
-        <v>6811337</v>
+        <v>6811562</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939279</v>
+        <v>125939226</v>
       </c>
       <c r="B41" t="n">
-        <v>78644</v>
+        <v>79595</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454802</v>
+        <v>454938</v>
       </c>
       <c r="R41" t="n">
-        <v>6811557</v>
+        <v>6811337</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B49" t="n">
-        <v>79595</v>
+        <v>78644</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R49" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B50" t="n">
-        <v>78644</v>
+        <v>79595</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R50" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939240</v>
+        <v>125939272</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454806</v>
+        <v>454896</v>
       </c>
       <c r="R2" t="n">
-        <v>6811636</v>
+        <v>6811450</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939272</v>
+        <v>125939240</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454896</v>
+        <v>454806</v>
       </c>
       <c r="R3" t="n">
-        <v>6811450</v>
+        <v>6811636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939282</v>
+        <v>125939247</v>
       </c>
       <c r="B4" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454870</v>
+        <v>454910</v>
       </c>
       <c r="R4" t="n">
-        <v>6811495</v>
+        <v>6811441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -929,7 +929,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939276</v>
+        <v>125939282</v>
       </c>
       <c r="B5" t="n">
-        <v>92532</v>
+        <v>78644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454947</v>
+        <v>454870</v>
       </c>
       <c r="R5" t="n">
-        <v>6811454</v>
+        <v>6811495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939247</v>
+        <v>125939276</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>92532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454910</v>
+        <v>454947</v>
       </c>
       <c r="R6" t="n">
-        <v>6811441</v>
+        <v>6811454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B18" t="n">
-        <v>78644</v>
+        <v>78735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R18" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B19" t="n">
-        <v>78735</v>
+        <v>78644</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R19" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939285</v>
+        <v>125939283</v>
       </c>
       <c r="B20" t="n">
-        <v>77926</v>
+        <v>78644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454930</v>
+        <v>454888</v>
       </c>
       <c r="R20" t="n">
-        <v>6811482</v>
+        <v>6811478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939238</v>
+        <v>125939285</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>77926</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,39 +2529,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454804</v>
+        <v>454930</v>
       </c>
       <c r="R21" t="n">
-        <v>6811564</v>
+        <v>6811482</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,7 +2578,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2594,11 +2589,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2625,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939283</v>
+        <v>125939238</v>
       </c>
       <c r="B22" t="n">
-        <v>78644</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,34 +2626,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454888</v>
+        <v>454804</v>
       </c>
       <c r="R22" t="n">
-        <v>6811478</v>
+        <v>6811564</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,7 +2680,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2696,6 +2691,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2819,45 +2819,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939262</v>
+        <v>125939233</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454710</v>
+        <v>454794</v>
       </c>
       <c r="R24" t="n">
-        <v>6811492</v>
+        <v>6811612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,7 +2921,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125939263</v>
+        <v>125939262</v>
       </c>
       <c r="B25" t="n">
         <v>78977</v>
@@ -2951,10 +2956,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454734</v>
+        <v>454710</v>
       </c>
       <c r="R25" t="n">
-        <v>6811565</v>
+        <v>6811492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,50 +3018,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939233</v>
+        <v>125939263</v>
       </c>
       <c r="B26" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454794</v>
+        <v>454734</v>
       </c>
       <c r="R26" t="n">
-        <v>6811612</v>
+        <v>6811565</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939247</v>
+        <v>125939282</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454910</v>
+        <v>454870</v>
       </c>
       <c r="R4" t="n">
-        <v>6811441</v>
+        <v>6811495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -929,7 +929,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939282</v>
+        <v>125939276</v>
       </c>
       <c r="B5" t="n">
-        <v>78644</v>
+        <v>92532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454870</v>
+        <v>454947</v>
       </c>
       <c r="R5" t="n">
-        <v>6811495</v>
+        <v>6811454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B6" t="n">
-        <v>92532</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R6" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125939217</v>
+        <v>125939256</v>
       </c>
       <c r="B7" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454837</v>
+        <v>454960</v>
       </c>
       <c r="R7" t="n">
-        <v>6811351</v>
+        <v>6811451</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939256</v>
+        <v>125939217</v>
       </c>
       <c r="B8" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454960</v>
+        <v>454837</v>
       </c>
       <c r="R8" t="n">
-        <v>6811451</v>
+        <v>6811351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939277</v>
+        <v>125939222</v>
       </c>
       <c r="B13" t="n">
-        <v>78644</v>
+        <v>79595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454907</v>
+        <v>454945</v>
       </c>
       <c r="R13" t="n">
-        <v>6811355</v>
+        <v>6811496</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939223</v>
+        <v>125939250</v>
       </c>
       <c r="B14" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454961</v>
+        <v>454931</v>
       </c>
       <c r="R14" t="n">
-        <v>6811450</v>
+        <v>6811462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939250</v>
+        <v>125939253</v>
       </c>
       <c r="B15" t="n">
         <v>78735</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454931</v>
+        <v>454880</v>
       </c>
       <c r="R15" t="n">
-        <v>6811462</v>
+        <v>6811541</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939222</v>
+        <v>125939223</v>
       </c>
       <c r="B16" t="n">
         <v>79595</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454945</v>
+        <v>454961</v>
       </c>
       <c r="R16" t="n">
-        <v>6811496</v>
+        <v>6811450</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939253</v>
+        <v>125939277</v>
       </c>
       <c r="B17" t="n">
-        <v>78735</v>
+        <v>78644</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454880</v>
+        <v>454907</v>
       </c>
       <c r="R17" t="n">
-        <v>6811541</v>
+        <v>6811355</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939283</v>
+        <v>125939246</v>
       </c>
       <c r="B20" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454888</v>
+        <v>454944</v>
       </c>
       <c r="R20" t="n">
-        <v>6811478</v>
+        <v>6811441</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939285</v>
+        <v>125939283</v>
       </c>
       <c r="B21" t="n">
-        <v>77926</v>
+        <v>78644</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454930</v>
+        <v>454888</v>
       </c>
       <c r="R21" t="n">
-        <v>6811482</v>
+        <v>6811478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939238</v>
+        <v>125939285</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>77926</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,39 +2626,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454804</v>
+        <v>454930</v>
       </c>
       <c r="R22" t="n">
-        <v>6811564</v>
+        <v>6811482</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,7 +2675,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2691,11 +2686,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939246</v>
+        <v>125939238</v>
       </c>
       <c r="B23" t="n">
-        <v>78736</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,34 +2723,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454944</v>
+        <v>454804</v>
       </c>
       <c r="R23" t="n">
-        <v>6811441</v>
+        <v>6811564</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,7 +2777,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2793,6 +2788,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2819,50 +2819,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939233</v>
+        <v>125939263</v>
       </c>
       <c r="B24" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454794</v>
+        <v>454734</v>
       </c>
       <c r="R24" t="n">
-        <v>6811612</v>
+        <v>6811565</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,45 +3013,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939263</v>
+        <v>125939233</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454734</v>
+        <v>454794</v>
       </c>
       <c r="R26" t="n">
-        <v>6811565</v>
+        <v>6811612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939270</v>
+        <v>125939228</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454944</v>
+        <v>454892</v>
       </c>
       <c r="R32" t="n">
-        <v>6811442</v>
+        <v>6811478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939224</v>
+        <v>125939245</v>
       </c>
       <c r="B33" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454899</v>
+        <v>454945</v>
       </c>
       <c r="R33" t="n">
-        <v>6811425</v>
+        <v>6811496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939221</v>
+        <v>125939270</v>
       </c>
       <c r="B34" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454868</v>
+        <v>454944</v>
       </c>
       <c r="R34" t="n">
-        <v>6811496</v>
+        <v>6811442</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939228</v>
+        <v>125939221</v>
       </c>
       <c r="B35" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454892</v>
+        <v>454868</v>
       </c>
       <c r="R35" t="n">
-        <v>6811478</v>
+        <v>6811496</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939245</v>
+        <v>125939224</v>
       </c>
       <c r="B36" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454945</v>
+        <v>454899</v>
       </c>
       <c r="R36" t="n">
-        <v>6811496</v>
+        <v>6811425</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939279</v>
+        <v>125939241</v>
       </c>
       <c r="B37" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4123,7 +4123,7 @@
         <v>454802</v>
       </c>
       <c r="R37" t="n">
-        <v>6811557</v>
+        <v>6811558</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939218</v>
+        <v>125939274</v>
       </c>
       <c r="B38" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454769</v>
+        <v>454933</v>
       </c>
       <c r="R38" t="n">
-        <v>6811673</v>
+        <v>6811343</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939274</v>
+        <v>125939226</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454933</v>
+        <v>454938</v>
       </c>
       <c r="R39" t="n">
-        <v>6811343</v>
+        <v>6811337</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939265</v>
+        <v>125939218</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454793</v>
+        <v>454769</v>
       </c>
       <c r="R40" t="n">
-        <v>6811562</v>
+        <v>6811673</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939226</v>
+        <v>125939265</v>
       </c>
       <c r="B41" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454938</v>
+        <v>454793</v>
       </c>
       <c r="R41" t="n">
-        <v>6811337</v>
+        <v>6811562</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939241</v>
+        <v>125939279</v>
       </c>
       <c r="B42" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4608,7 +4608,7 @@
         <v>454802</v>
       </c>
       <c r="R42" t="n">
-        <v>6811558</v>
+        <v>6811557</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939229</v>
+        <v>125939264</v>
       </c>
       <c r="B45" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454945</v>
+        <v>454788</v>
       </c>
       <c r="R45" t="n">
-        <v>6811496</v>
+        <v>6811599</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939264</v>
+        <v>125939257</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454788</v>
+        <v>454910</v>
       </c>
       <c r="R47" t="n">
-        <v>6811599</v>
+        <v>6811442</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5152,10 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125939257</v>
+        <v>125939229</v>
       </c>
       <c r="B48" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454910</v>
+        <v>454945</v>
       </c>
       <c r="R48" t="n">
-        <v>6811442</v>
+        <v>6811496</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B49" t="n">
-        <v>78644</v>
+        <v>79595</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R49" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B50" t="n">
-        <v>79595</v>
+        <v>78644</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R50" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939260</v>
+        <v>125939271</v>
       </c>
       <c r="B52" t="n">
         <v>78977</v>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454706</v>
+        <v>454943</v>
       </c>
       <c r="R52" t="n">
-        <v>6811484</v>
+        <v>6811446</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939251</v>
+        <v>125939248</v>
       </c>
       <c r="B53" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454806</v>
+        <v>454938</v>
       </c>
       <c r="R53" t="n">
-        <v>6811636</v>
+        <v>6811339</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5734,7 +5734,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939271</v>
+        <v>125939260</v>
       </c>
       <c r="B54" t="n">
         <v>78977</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454943</v>
+        <v>454706</v>
       </c>
       <c r="R54" t="n">
-        <v>6811446</v>
+        <v>6811484</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5928,10 +5928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939248</v>
+        <v>125939251</v>
       </c>
       <c r="B56" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454938</v>
+        <v>454806</v>
       </c>
       <c r="R56" t="n">
-        <v>6811339</v>
+        <v>6811636</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939282</v>
+        <v>125939247</v>
       </c>
       <c r="B4" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454870</v>
+        <v>454910</v>
       </c>
       <c r="R4" t="n">
-        <v>6811495</v>
+        <v>6811441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -929,7 +929,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939276</v>
+        <v>125939282</v>
       </c>
       <c r="B5" t="n">
-        <v>92532</v>
+        <v>78644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454947</v>
+        <v>454870</v>
       </c>
       <c r="R5" t="n">
-        <v>6811454</v>
+        <v>6811495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939247</v>
+        <v>125939276</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>92532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454910</v>
+        <v>454947</v>
       </c>
       <c r="R6" t="n">
-        <v>6811441</v>
+        <v>6811454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2819,45 +2819,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939263</v>
+        <v>125939233</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454734</v>
+        <v>454794</v>
       </c>
       <c r="R24" t="n">
-        <v>6811565</v>
+        <v>6811612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,7 +2921,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125939262</v>
+        <v>125939263</v>
       </c>
       <c r="B25" t="n">
         <v>78977</v>
@@ -2951,10 +2956,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454710</v>
+        <v>454734</v>
       </c>
       <c r="R25" t="n">
-        <v>6811492</v>
+        <v>6811565</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,50 +3018,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939233</v>
+        <v>125939262</v>
       </c>
       <c r="B26" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454794</v>
+        <v>454710</v>
       </c>
       <c r="R26" t="n">
-        <v>6811612</v>
+        <v>6811492</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125939272</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125939240</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939247</v>
+        <v>125939276</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>92535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454910</v>
+        <v>454947</v>
       </c>
       <c r="R4" t="n">
-        <v>6811441</v>
+        <v>6811454</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>125939282</v>
       </c>
       <c r="B5" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B6" t="n">
-        <v>92532</v>
+        <v>78739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R6" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125939256</v>
+        <v>125939217</v>
       </c>
       <c r="B7" t="n">
-        <v>78735</v>
+        <v>79598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454960</v>
+        <v>454837</v>
       </c>
       <c r="R7" t="n">
-        <v>6811451</v>
+        <v>6811351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939217</v>
+        <v>125939256</v>
       </c>
       <c r="B8" t="n">
-        <v>79595</v>
+        <v>78738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454837</v>
+        <v>454960</v>
       </c>
       <c r="R8" t="n">
-        <v>6811351</v>
+        <v>6811451</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939286</v>
+        <v>125939278</v>
       </c>
       <c r="B9" t="n">
-        <v>78383</v>
+        <v>78647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454835</v>
+        <v>454854</v>
       </c>
       <c r="R9" t="n">
-        <v>6811352</v>
+        <v>6811347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939278</v>
+        <v>125939286</v>
       </c>
       <c r="B10" t="n">
-        <v>78644</v>
+        <v>78386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454854</v>
+        <v>454835</v>
       </c>
       <c r="R10" t="n">
-        <v>6811347</v>
+        <v>6811352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939243</v>
+        <v>125939250</v>
       </c>
       <c r="B11" t="n">
-        <v>78736</v>
+        <v>78738</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454896</v>
+        <v>454931</v>
       </c>
       <c r="R11" t="n">
-        <v>6811477</v>
+        <v>6811462</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939230</v>
+        <v>125939253</v>
       </c>
       <c r="B12" t="n">
-        <v>79566</v>
+        <v>78738</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454944</v>
+        <v>454880</v>
       </c>
       <c r="R12" t="n">
-        <v>6811441</v>
+        <v>6811541</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939222</v>
+        <v>125939277</v>
       </c>
       <c r="B13" t="n">
-        <v>79595</v>
+        <v>78647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454945</v>
+        <v>454907</v>
       </c>
       <c r="R13" t="n">
-        <v>6811496</v>
+        <v>6811355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939250</v>
+        <v>125939243</v>
       </c>
       <c r="B14" t="n">
-        <v>78735</v>
+        <v>78739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454931</v>
+        <v>454896</v>
       </c>
       <c r="R14" t="n">
-        <v>6811462</v>
+        <v>6811477</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939253</v>
+        <v>125939230</v>
       </c>
       <c r="B15" t="n">
-        <v>78735</v>
+        <v>79569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454880</v>
+        <v>454944</v>
       </c>
       <c r="R15" t="n">
-        <v>6811541</v>
+        <v>6811441</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939223</v>
+        <v>125939222</v>
       </c>
       <c r="B16" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454961</v>
+        <v>454945</v>
       </c>
       <c r="R16" t="n">
-        <v>6811450</v>
+        <v>6811496</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939277</v>
+        <v>125939223</v>
       </c>
       <c r="B17" t="n">
-        <v>78644</v>
+        <v>79598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454907</v>
+        <v>454961</v>
       </c>
       <c r="R17" t="n">
-        <v>6811355</v>
+        <v>6811450</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B18" t="n">
-        <v>78735</v>
+        <v>78647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R18" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B19" t="n">
-        <v>78644</v>
+        <v>78738</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R19" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939246</v>
+        <v>125939238</v>
       </c>
       <c r="B20" t="n">
-        <v>78736</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,34 +2432,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454944</v>
+        <v>454804</v>
       </c>
       <c r="R20" t="n">
-        <v>6811441</v>
+        <v>6811564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2481,7 +2486,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2492,6 +2497,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2521,7 +2531,7 @@
         <v>125939283</v>
       </c>
       <c r="B21" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939285</v>
+        <v>125939246</v>
       </c>
       <c r="B22" t="n">
-        <v>77926</v>
+        <v>78739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454930</v>
+        <v>454944</v>
       </c>
       <c r="R22" t="n">
-        <v>6811482</v>
+        <v>6811441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939238</v>
+        <v>125939285</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>77929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,39 +2733,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454804</v>
+        <v>454930</v>
       </c>
       <c r="R23" t="n">
-        <v>6811564</v>
+        <v>6811482</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2777,7 +2782,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2788,11 +2793,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2819,50 +2819,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939233</v>
+        <v>125939262</v>
       </c>
       <c r="B24" t="n">
-        <v>56848</v>
+        <v>78980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454794</v>
+        <v>454710</v>
       </c>
       <c r="R24" t="n">
-        <v>6811612</v>
+        <v>6811492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2924,7 +2919,7 @@
         <v>125939263</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3018,45 +3013,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939262</v>
+        <v>125939233</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>56849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454710</v>
+        <v>454794</v>
       </c>
       <c r="R26" t="n">
-        <v>6811492</v>
+        <v>6811612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
         <v>125939242</v>
       </c>
       <c r="B27" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>125939273</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>125939269</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939231</v>
+        <v>125939221</v>
       </c>
       <c r="B30" t="n">
-        <v>79072</v>
+        <v>79598</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454930</v>
+        <v>454868</v>
       </c>
       <c r="R30" t="n">
-        <v>6811482</v>
+        <v>6811496</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939281</v>
+        <v>125939224</v>
       </c>
       <c r="B31" t="n">
-        <v>78644</v>
+        <v>79598</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454865</v>
+        <v>454899</v>
       </c>
       <c r="R31" t="n">
-        <v>6811503</v>
+        <v>6811425</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939228</v>
+        <v>125939270</v>
       </c>
       <c r="B32" t="n">
-        <v>79566</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454892</v>
+        <v>454944</v>
       </c>
       <c r="R32" t="n">
-        <v>6811478</v>
+        <v>6811442</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939245</v>
+        <v>125939231</v>
       </c>
       <c r="B33" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454945</v>
+        <v>454930</v>
       </c>
       <c r="R33" t="n">
-        <v>6811496</v>
+        <v>6811482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939270</v>
+        <v>125939281</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>78647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454944</v>
+        <v>454865</v>
       </c>
       <c r="R34" t="n">
-        <v>6811442</v>
+        <v>6811503</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939221</v>
+        <v>125939228</v>
       </c>
       <c r="B35" t="n">
-        <v>79595</v>
+        <v>79569</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454868</v>
+        <v>454892</v>
       </c>
       <c r="R35" t="n">
-        <v>6811496</v>
+        <v>6811478</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939224</v>
+        <v>125939245</v>
       </c>
       <c r="B36" t="n">
-        <v>79595</v>
+        <v>78739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454899</v>
+        <v>454945</v>
       </c>
       <c r="R36" t="n">
-        <v>6811425</v>
+        <v>6811496</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939241</v>
+        <v>125939274</v>
       </c>
       <c r="B37" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454802</v>
+        <v>454933</v>
       </c>
       <c r="R37" t="n">
-        <v>6811558</v>
+        <v>6811343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939274</v>
+        <v>125939265</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454933</v>
+        <v>454793</v>
       </c>
       <c r="R38" t="n">
-        <v>6811343</v>
+        <v>6811562</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939226</v>
+        <v>125939241</v>
       </c>
       <c r="B39" t="n">
-        <v>79595</v>
+        <v>78739</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454938</v>
+        <v>454802</v>
       </c>
       <c r="R39" t="n">
-        <v>6811337</v>
+        <v>6811558</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939218</v>
+        <v>125939226</v>
       </c>
       <c r="B40" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454769</v>
+        <v>454938</v>
       </c>
       <c r="R40" t="n">
-        <v>6811673</v>
+        <v>6811337</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939265</v>
+        <v>125939218</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454793</v>
+        <v>454769</v>
       </c>
       <c r="R41" t="n">
-        <v>6811562</v>
+        <v>6811673</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4573,7 +4573,7 @@
         <v>125939279</v>
       </c>
       <c r="B42" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>125939266</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>125939227</v>
       </c>
       <c r="B44" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939264</v>
+        <v>125939219</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454788</v>
+        <v>454849</v>
       </c>
       <c r="R45" t="n">
-        <v>6811599</v>
+        <v>6811570</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939219</v>
+        <v>125939264</v>
       </c>
       <c r="B46" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4969,21 +4969,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454849</v>
+        <v>454788</v>
       </c>
       <c r="R46" t="n">
-        <v>6811570</v>
+        <v>6811599</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5058,7 +5058,7 @@
         <v>125939257</v>
       </c>
       <c r="B47" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>125939229</v>
       </c>
       <c r="B48" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939225</v>
+        <v>125939284</v>
       </c>
       <c r="B49" t="n">
-        <v>79595</v>
+        <v>78647</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R49" t="n">
-        <v>6811384</v>
+        <v>6811430</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939284</v>
+        <v>125939225</v>
       </c>
       <c r="B50" t="n">
-        <v>78644</v>
+        <v>79598</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454896</v>
+        <v>454951</v>
       </c>
       <c r="R50" t="n">
-        <v>6811430</v>
+        <v>6811384</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5446,7 +5446,7 @@
         <v>125939267</v>
       </c>
       <c r="B51" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939271</v>
+        <v>125939248</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454943</v>
+        <v>454938</v>
       </c>
       <c r="R52" t="n">
-        <v>6811446</v>
+        <v>6811339</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939248</v>
+        <v>125939260</v>
       </c>
       <c r="B53" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454938</v>
+        <v>454706</v>
       </c>
       <c r="R53" t="n">
-        <v>6811339</v>
+        <v>6811484</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5734,10 +5734,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939260</v>
+        <v>125939251</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5745,21 +5745,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454706</v>
+        <v>454806</v>
       </c>
       <c r="R54" t="n">
-        <v>6811484</v>
+        <v>6811636</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5831,10 +5831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939268</v>
+        <v>125939271</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454882</v>
+        <v>454943</v>
       </c>
       <c r="R55" t="n">
-        <v>6811551</v>
+        <v>6811446</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939251</v>
+        <v>125939268</v>
       </c>
       <c r="B56" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454806</v>
+        <v>454882</v>
       </c>
       <c r="R56" t="n">
-        <v>6811636</v>
+        <v>6811551</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -6028,7 +6028,7 @@
         <v>125939232</v>
       </c>
       <c r="B57" t="n">
-        <v>91527</v>
+        <v>91530</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125939217</v>
+        <v>125939256</v>
       </c>
       <c r="B7" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454837</v>
+        <v>454960</v>
       </c>
       <c r="R7" t="n">
-        <v>6811351</v>
+        <v>6811451</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939256</v>
+        <v>125939217</v>
       </c>
       <c r="B8" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454960</v>
+        <v>454837</v>
       </c>
       <c r="R8" t="n">
-        <v>6811451</v>
+        <v>6811351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939250</v>
+        <v>125939222</v>
       </c>
       <c r="B11" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454931</v>
+        <v>454945</v>
       </c>
       <c r="R11" t="n">
-        <v>6811462</v>
+        <v>6811496</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939253</v>
+        <v>125939223</v>
       </c>
       <c r="B12" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454880</v>
+        <v>454961</v>
       </c>
       <c r="R12" t="n">
-        <v>6811541</v>
+        <v>6811450</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939277</v>
+        <v>125939250</v>
       </c>
       <c r="B13" t="n">
-        <v>78647</v>
+        <v>78738</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454907</v>
+        <v>454931</v>
       </c>
       <c r="R13" t="n">
-        <v>6811355</v>
+        <v>6811462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939243</v>
+        <v>125939253</v>
       </c>
       <c r="B14" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454896</v>
+        <v>454880</v>
       </c>
       <c r="R14" t="n">
-        <v>6811477</v>
+        <v>6811541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939230</v>
+        <v>125939277</v>
       </c>
       <c r="B15" t="n">
-        <v>79569</v>
+        <v>78647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454944</v>
+        <v>454907</v>
       </c>
       <c r="R15" t="n">
-        <v>6811441</v>
+        <v>6811355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939222</v>
+        <v>125939243</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454945</v>
+        <v>454896</v>
       </c>
       <c r="R16" t="n">
-        <v>6811496</v>
+        <v>6811477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939223</v>
+        <v>125939230</v>
       </c>
       <c r="B17" t="n">
-        <v>79598</v>
+        <v>79569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454961</v>
+        <v>454944</v>
       </c>
       <c r="R17" t="n">
-        <v>6811450</v>
+        <v>6811441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939262</v>
+        <v>125939242</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454710</v>
+        <v>454883</v>
       </c>
       <c r="R24" t="n">
-        <v>6811492</v>
+        <v>6811548</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125939263</v>
+        <v>125939262</v>
       </c>
       <c r="B25" t="n">
         <v>78980</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454734</v>
+        <v>454710</v>
       </c>
       <c r="R25" t="n">
-        <v>6811565</v>
+        <v>6811492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,50 +3013,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939233</v>
+        <v>125939263</v>
       </c>
       <c r="B26" t="n">
-        <v>56849</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454794</v>
+        <v>454734</v>
       </c>
       <c r="R26" t="n">
-        <v>6811612</v>
+        <v>6811565</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3115,45 +3110,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125939242</v>
+        <v>125939233</v>
       </c>
       <c r="B27" t="n">
-        <v>78739</v>
+        <v>56849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454883</v>
+        <v>454794</v>
       </c>
       <c r="R27" t="n">
-        <v>6811548</v>
+        <v>6811612</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B4" t="n">
-        <v>92535</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R4" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939247</v>
+        <v>125939276</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>92535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454910</v>
+        <v>454947</v>
       </c>
       <c r="R6" t="n">
-        <v>6811441</v>
+        <v>6811454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125939256</v>
+        <v>125939217</v>
       </c>
       <c r="B7" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454960</v>
+        <v>454837</v>
       </c>
       <c r="R7" t="n">
-        <v>6811451</v>
+        <v>6811351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939217</v>
+        <v>125939256</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454837</v>
+        <v>454960</v>
       </c>
       <c r="R8" t="n">
-        <v>6811351</v>
+        <v>6811451</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939222</v>
+        <v>125939223</v>
       </c>
       <c r="B11" t="n">
         <v>79598</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454945</v>
+        <v>454961</v>
       </c>
       <c r="R11" t="n">
-        <v>6811496</v>
+        <v>6811450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939223</v>
+        <v>125939222</v>
       </c>
       <c r="B12" t="n">
         <v>79598</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454961</v>
+        <v>454945</v>
       </c>
       <c r="R12" t="n">
-        <v>6811450</v>
+        <v>6811496</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B18" t="n">
-        <v>78647</v>
+        <v>78738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R18" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B19" t="n">
-        <v>78738</v>
+        <v>78647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R19" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939238</v>
+        <v>125939285</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>77929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,39 +2432,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454804</v>
+        <v>454930</v>
       </c>
       <c r="R20" t="n">
-        <v>6811564</v>
+        <v>6811482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2486,7 +2481,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2497,11 +2492,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2625,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939246</v>
+        <v>125939238</v>
       </c>
       <c r="B22" t="n">
-        <v>78739</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,34 +2626,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454944</v>
+        <v>454804</v>
       </c>
       <c r="R22" t="n">
-        <v>6811441</v>
+        <v>6811564</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,7 +2680,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2696,6 +2691,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939285</v>
+        <v>125939246</v>
       </c>
       <c r="B23" t="n">
-        <v>77929</v>
+        <v>78739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454930</v>
+        <v>454944</v>
       </c>
       <c r="R23" t="n">
-        <v>6811482</v>
+        <v>6811441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939221</v>
+        <v>125939270</v>
       </c>
       <c r="B30" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454868</v>
+        <v>454944</v>
       </c>
       <c r="R30" t="n">
-        <v>6811496</v>
+        <v>6811442</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939224</v>
+        <v>125939231</v>
       </c>
       <c r="B31" t="n">
-        <v>79598</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454899</v>
+        <v>454930</v>
       </c>
       <c r="R31" t="n">
-        <v>6811425</v>
+        <v>6811482</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939270</v>
+        <v>125939228</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454944</v>
+        <v>454892</v>
       </c>
       <c r="R32" t="n">
-        <v>6811442</v>
+        <v>6811478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939231</v>
+        <v>125939245</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>78739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454930</v>
+        <v>454945</v>
       </c>
       <c r="R33" t="n">
-        <v>6811482</v>
+        <v>6811496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939228</v>
+        <v>125939224</v>
       </c>
       <c r="B35" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454892</v>
+        <v>454899</v>
       </c>
       <c r="R35" t="n">
-        <v>6811478</v>
+        <v>6811425</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939245</v>
+        <v>125939221</v>
       </c>
       <c r="B36" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454945</v>
+        <v>454868</v>
       </c>
       <c r="R36" t="n">
         <v>6811496</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939274</v>
+        <v>125939279</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>78647</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454933</v>
+        <v>454802</v>
       </c>
       <c r="R37" t="n">
-        <v>6811343</v>
+        <v>6811557</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939265</v>
+        <v>125939218</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454793</v>
+        <v>454769</v>
       </c>
       <c r="R38" t="n">
-        <v>6811562</v>
+        <v>6811673</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939241</v>
+        <v>125939274</v>
       </c>
       <c r="B39" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454802</v>
+        <v>454933</v>
       </c>
       <c r="R39" t="n">
-        <v>6811558</v>
+        <v>6811343</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939226</v>
+        <v>125939265</v>
       </c>
       <c r="B40" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454938</v>
+        <v>454793</v>
       </c>
       <c r="R40" t="n">
-        <v>6811337</v>
+        <v>6811562</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4473,7 +4473,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939218</v>
+        <v>125939226</v>
       </c>
       <c r="B41" t="n">
         <v>79598</v>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454769</v>
+        <v>454938</v>
       </c>
       <c r="R41" t="n">
-        <v>6811673</v>
+        <v>6811337</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939279</v>
+        <v>125939241</v>
       </c>
       <c r="B42" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4608,7 +4608,7 @@
         <v>454802</v>
       </c>
       <c r="R42" t="n">
-        <v>6811557</v>
+        <v>6811558</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939248</v>
+        <v>125939260</v>
       </c>
       <c r="B52" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454938</v>
+        <v>454706</v>
       </c>
       <c r="R52" t="n">
-        <v>6811339</v>
+        <v>6811484</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5637,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939260</v>
+        <v>125939251</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454706</v>
+        <v>454806</v>
       </c>
       <c r="R53" t="n">
-        <v>6811484</v>
+        <v>6811636</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939251</v>
+        <v>125939271</v>
       </c>
       <c r="B54" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5745,21 +5745,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454806</v>
+        <v>454943</v>
       </c>
       <c r="R54" t="n">
-        <v>6811636</v>
+        <v>6811446</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -5831,7 +5831,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939271</v>
+        <v>125939268</v>
       </c>
       <c r="B55" t="n">
         <v>78980</v>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454943</v>
+        <v>454882</v>
       </c>
       <c r="R55" t="n">
-        <v>6811446</v>
+        <v>6811551</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5928,10 +5928,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939268</v>
+        <v>125939248</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454882</v>
+        <v>454938</v>
       </c>
       <c r="R56" t="n">
-        <v>6811551</v>
+        <v>6811339</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B18" t="n">
-        <v>78738</v>
+        <v>78647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R18" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B19" t="n">
-        <v>78647</v>
+        <v>78738</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R19" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939285</v>
+        <v>125939238</v>
       </c>
       <c r="B20" t="n">
-        <v>77929</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,34 +2432,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454930</v>
+        <v>454804</v>
       </c>
       <c r="R20" t="n">
-        <v>6811482</v>
+        <v>6811564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2481,7 +2486,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2492,6 +2497,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2518,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939283</v>
+        <v>125939246</v>
       </c>
       <c r="B21" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454888</v>
+        <v>454944</v>
       </c>
       <c r="R21" t="n">
-        <v>6811478</v>
+        <v>6811441</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939238</v>
+        <v>125939283</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>78647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,39 +2636,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454804</v>
+        <v>454888</v>
       </c>
       <c r="R22" t="n">
-        <v>6811564</v>
+        <v>6811478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,7 +2685,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2691,11 +2696,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939246</v>
+        <v>125939285</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>77929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454944</v>
+        <v>454930</v>
       </c>
       <c r="R23" t="n">
-        <v>6811441</v>
+        <v>6811482</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939228</v>
+        <v>125939281</v>
       </c>
       <c r="B32" t="n">
-        <v>79569</v>
+        <v>78647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454892</v>
+        <v>454865</v>
       </c>
       <c r="R32" t="n">
-        <v>6811478</v>
+        <v>6811503</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939245</v>
+        <v>125939224</v>
       </c>
       <c r="B33" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454945</v>
+        <v>454899</v>
       </c>
       <c r="R33" t="n">
-        <v>6811496</v>
+        <v>6811425</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939281</v>
+        <v>125939221</v>
       </c>
       <c r="B34" t="n">
-        <v>78647</v>
+        <v>79598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454865</v>
+        <v>454868</v>
       </c>
       <c r="R34" t="n">
-        <v>6811503</v>
+        <v>6811496</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939224</v>
+        <v>125939228</v>
       </c>
       <c r="B35" t="n">
-        <v>79598</v>
+        <v>79569</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454899</v>
+        <v>454892</v>
       </c>
       <c r="R35" t="n">
-        <v>6811425</v>
+        <v>6811478</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939221</v>
+        <v>125939245</v>
       </c>
       <c r="B36" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454868</v>
+        <v>454945</v>
       </c>
       <c r="R36" t="n">
         <v>6811496</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939279</v>
+        <v>125939241</v>
       </c>
       <c r="B37" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4123,7 +4123,7 @@
         <v>454802</v>
       </c>
       <c r="R37" t="n">
-        <v>6811557</v>
+        <v>6811558</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939218</v>
+        <v>125939279</v>
       </c>
       <c r="B38" t="n">
-        <v>79598</v>
+        <v>78647</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454769</v>
+        <v>454802</v>
       </c>
       <c r="R38" t="n">
-        <v>6811673</v>
+        <v>6811557</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939274</v>
+        <v>125939218</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454933</v>
+        <v>454769</v>
       </c>
       <c r="R39" t="n">
-        <v>6811343</v>
+        <v>6811673</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4376,7 +4376,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939265</v>
+        <v>125939274</v>
       </c>
       <c r="B40" t="n">
         <v>78980</v>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454793</v>
+        <v>454933</v>
       </c>
       <c r="R40" t="n">
-        <v>6811562</v>
+        <v>6811343</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939226</v>
+        <v>125939265</v>
       </c>
       <c r="B41" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454938</v>
+        <v>454793</v>
       </c>
       <c r="R41" t="n">
-        <v>6811337</v>
+        <v>6811562</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939241</v>
+        <v>125939226</v>
       </c>
       <c r="B42" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454802</v>
+        <v>454938</v>
       </c>
       <c r="R42" t="n">
-        <v>6811558</v>
+        <v>6811337</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939247</v>
+        <v>125939282</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454910</v>
+        <v>454870</v>
       </c>
       <c r="R4" t="n">
-        <v>6811441</v>
+        <v>6811495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -929,7 +929,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939282</v>
+        <v>125939276</v>
       </c>
       <c r="B5" t="n">
-        <v>78647</v>
+        <v>92535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454870</v>
+        <v>454947</v>
       </c>
       <c r="R5" t="n">
-        <v>6811495</v>
+        <v>6811454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939276</v>
+        <v>125939247</v>
       </c>
       <c r="B6" t="n">
-        <v>92535</v>
+        <v>78739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454947</v>
+        <v>454910</v>
       </c>
       <c r="R6" t="n">
-        <v>6811454</v>
+        <v>6811441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939223</v>
+        <v>125939277</v>
       </c>
       <c r="B11" t="n">
-        <v>79598</v>
+        <v>78647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454961</v>
+        <v>454907</v>
       </c>
       <c r="R11" t="n">
-        <v>6811450</v>
+        <v>6811355</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939222</v>
+        <v>125939223</v>
       </c>
       <c r="B12" t="n">
         <v>79598</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454945</v>
+        <v>454961</v>
       </c>
       <c r="R12" t="n">
-        <v>6811496</v>
+        <v>6811450</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939250</v>
+        <v>125939222</v>
       </c>
       <c r="B13" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454931</v>
+        <v>454945</v>
       </c>
       <c r="R13" t="n">
-        <v>6811462</v>
+        <v>6811496</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939253</v>
+        <v>125939250</v>
       </c>
       <c r="B14" t="n">
         <v>78738</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454880</v>
+        <v>454931</v>
       </c>
       <c r="R14" t="n">
-        <v>6811541</v>
+        <v>6811462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939277</v>
+        <v>125939253</v>
       </c>
       <c r="B15" t="n">
-        <v>78647</v>
+        <v>78738</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454907</v>
+        <v>454880</v>
       </c>
       <c r="R15" t="n">
-        <v>6811355</v>
+        <v>6811541</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B18" t="n">
-        <v>78647</v>
+        <v>78738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R18" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B19" t="n">
-        <v>78738</v>
+        <v>78647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R19" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939238</v>
+        <v>125939285</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>77929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,39 +2432,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454804</v>
+        <v>454930</v>
       </c>
       <c r="R20" t="n">
-        <v>6811564</v>
+        <v>6811482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2486,7 +2481,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2497,11 +2492,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2528,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939246</v>
+        <v>125939283</v>
       </c>
       <c r="B21" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2539,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454944</v>
+        <v>454888</v>
       </c>
       <c r="R21" t="n">
-        <v>6811441</v>
+        <v>6811478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2625,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939283</v>
+        <v>125939238</v>
       </c>
       <c r="B22" t="n">
-        <v>78647</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,34 +2626,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454888</v>
+        <v>454804</v>
       </c>
       <c r="R22" t="n">
-        <v>6811478</v>
+        <v>6811564</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,7 +2680,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2696,6 +2691,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939285</v>
+        <v>125939246</v>
       </c>
       <c r="B23" t="n">
-        <v>77929</v>
+        <v>78739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454930</v>
+        <v>454944</v>
       </c>
       <c r="R23" t="n">
-        <v>6811482</v>
+        <v>6811441</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939281</v>
+        <v>125939228</v>
       </c>
       <c r="B32" t="n">
-        <v>78647</v>
+        <v>79569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454865</v>
+        <v>454892</v>
       </c>
       <c r="R32" t="n">
-        <v>6811503</v>
+        <v>6811478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939224</v>
+        <v>125939245</v>
       </c>
       <c r="B33" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454899</v>
+        <v>454945</v>
       </c>
       <c r="R33" t="n">
-        <v>6811425</v>
+        <v>6811496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939221</v>
+        <v>125939281</v>
       </c>
       <c r="B34" t="n">
-        <v>79598</v>
+        <v>78647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454868</v>
+        <v>454865</v>
       </c>
       <c r="R34" t="n">
-        <v>6811496</v>
+        <v>6811503</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939228</v>
+        <v>125939224</v>
       </c>
       <c r="B35" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454892</v>
+        <v>454899</v>
       </c>
       <c r="R35" t="n">
-        <v>6811478</v>
+        <v>6811425</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939245</v>
+        <v>125939221</v>
       </c>
       <c r="B36" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454945</v>
+        <v>454868</v>
       </c>
       <c r="R36" t="n">
         <v>6811496</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939282</v>
+        <v>125939247</v>
       </c>
       <c r="B4" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454870</v>
+        <v>454910</v>
       </c>
       <c r="R4" t="n">
-        <v>6811495</v>
+        <v>6811441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -929,7 +929,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939276</v>
+        <v>125939282</v>
       </c>
       <c r="B5" t="n">
-        <v>92535</v>
+        <v>78647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454947</v>
+        <v>454870</v>
       </c>
       <c r="R5" t="n">
-        <v>6811454</v>
+        <v>6811495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939247</v>
+        <v>125939276</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>92535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454910</v>
+        <v>454947</v>
       </c>
       <c r="R6" t="n">
-        <v>6811441</v>
+        <v>6811454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939277</v>
+        <v>125939223</v>
       </c>
       <c r="B11" t="n">
-        <v>78647</v>
+        <v>79598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454907</v>
+        <v>454961</v>
       </c>
       <c r="R11" t="n">
-        <v>6811355</v>
+        <v>6811450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939223</v>
+        <v>125939222</v>
       </c>
       <c r="B12" t="n">
         <v>79598</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454961</v>
+        <v>454945</v>
       </c>
       <c r="R12" t="n">
-        <v>6811450</v>
+        <v>6811496</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939222</v>
+        <v>125939250</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454945</v>
+        <v>454931</v>
       </c>
       <c r="R13" t="n">
-        <v>6811496</v>
+        <v>6811462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939250</v>
+        <v>125939253</v>
       </c>
       <c r="B14" t="n">
         <v>78738</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454931</v>
+        <v>454880</v>
       </c>
       <c r="R14" t="n">
-        <v>6811462</v>
+        <v>6811541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939253</v>
+        <v>125939277</v>
       </c>
       <c r="B15" t="n">
-        <v>78738</v>
+        <v>78647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454880</v>
+        <v>454907</v>
       </c>
       <c r="R15" t="n">
-        <v>6811541</v>
+        <v>6811355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939254</v>
+        <v>125939280</v>
       </c>
       <c r="B18" t="n">
-        <v>78738</v>
+        <v>78647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454943</v>
+        <v>454809</v>
       </c>
       <c r="R18" t="n">
-        <v>6811500</v>
+        <v>6811578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939280</v>
+        <v>125939254</v>
       </c>
       <c r="B19" t="n">
-        <v>78647</v>
+        <v>78738</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454809</v>
+        <v>454943</v>
       </c>
       <c r="R19" t="n">
-        <v>6811578</v>
+        <v>6811500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939285</v>
+        <v>125939238</v>
       </c>
       <c r="B20" t="n">
-        <v>77929</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,34 +2432,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454930</v>
+        <v>454804</v>
       </c>
       <c r="R20" t="n">
-        <v>6811482</v>
+        <v>6811564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2481,7 +2486,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2492,6 +2497,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2518,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939283</v>
+        <v>125939246</v>
       </c>
       <c r="B21" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454888</v>
+        <v>454944</v>
       </c>
       <c r="R21" t="n">
-        <v>6811478</v>
+        <v>6811441</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939238</v>
+        <v>125939283</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>78647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,39 +2636,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454804</v>
+        <v>454888</v>
       </c>
       <c r="R22" t="n">
-        <v>6811564</v>
+        <v>6811478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,7 +2685,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2691,11 +2696,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939246</v>
+        <v>125939285</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>77929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454944</v>
+        <v>454930</v>
       </c>
       <c r="R23" t="n">
-        <v>6811441</v>
+        <v>6811482</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939228</v>
+        <v>125939281</v>
       </c>
       <c r="B32" t="n">
-        <v>79569</v>
+        <v>78647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454892</v>
+        <v>454865</v>
       </c>
       <c r="R32" t="n">
-        <v>6811478</v>
+        <v>6811503</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939245</v>
+        <v>125939224</v>
       </c>
       <c r="B33" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454945</v>
+        <v>454899</v>
       </c>
       <c r="R33" t="n">
-        <v>6811496</v>
+        <v>6811425</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939281</v>
+        <v>125939221</v>
       </c>
       <c r="B34" t="n">
-        <v>78647</v>
+        <v>79598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454865</v>
+        <v>454868</v>
       </c>
       <c r="R34" t="n">
-        <v>6811503</v>
+        <v>6811496</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939224</v>
+        <v>125939228</v>
       </c>
       <c r="B35" t="n">
-        <v>79598</v>
+        <v>79569</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3902,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454899</v>
+        <v>454892</v>
       </c>
       <c r="R35" t="n">
-        <v>6811425</v>
+        <v>6811478</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939221</v>
+        <v>125939245</v>
       </c>
       <c r="B36" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454868</v>
+        <v>454945</v>
       </c>
       <c r="R36" t="n">
         <v>6811496</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125939272</v>
+        <v>125939232</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>92198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454896</v>
+        <v>454788</v>
       </c>
       <c r="R2" t="n">
-        <v>6811450</v>
+        <v>6811611</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -748,12 +748,18 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Behöver mikroskoperas</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125939240</v>
+        <v>125939277</v>
       </c>
       <c r="B3" t="n">
-        <v>78739</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +789,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454806</v>
+        <v>454907</v>
       </c>
       <c r="R3" t="n">
-        <v>6811636</v>
+        <v>6811355</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +838,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125939247</v>
+        <v>125939278</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +886,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454910</v>
+        <v>454854</v>
       </c>
       <c r="R4" t="n">
-        <v>6811441</v>
+        <v>6811347</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -929,7 +935,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -966,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125939282</v>
+        <v>125939279</v>
       </c>
       <c r="B5" t="n">
-        <v>78647</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454870</v>
+        <v>454802</v>
       </c>
       <c r="R5" t="n">
-        <v>6811495</v>
+        <v>6811557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1069,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125939276</v>
+        <v>125939280</v>
       </c>
       <c r="B6" t="n">
-        <v>92535</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454947</v>
+        <v>454809</v>
       </c>
       <c r="R6" t="n">
-        <v>6811454</v>
+        <v>6811578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1123,7 +1129,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1160,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125939217</v>
+        <v>125939281</v>
       </c>
       <c r="B7" t="n">
-        <v>79598</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454837</v>
+        <v>454865</v>
       </c>
       <c r="R7" t="n">
-        <v>6811351</v>
+        <v>6811503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125939256</v>
+        <v>125939282</v>
       </c>
       <c r="B8" t="n">
-        <v>78738</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1298,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454960</v>
+        <v>454870</v>
       </c>
       <c r="R8" t="n">
-        <v>6811451</v>
+        <v>6811495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1317,7 +1323,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1354,10 +1360,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125939278</v>
+        <v>125939283</v>
       </c>
       <c r="B9" t="n">
-        <v>78647</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454854</v>
+        <v>454888</v>
       </c>
       <c r="R9" t="n">
-        <v>6811347</v>
+        <v>6811478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1414,7 +1420,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1451,10 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125939286</v>
+        <v>125939284</v>
       </c>
       <c r="B10" t="n">
-        <v>78386</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1468,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454835</v>
+        <v>454896</v>
       </c>
       <c r="R10" t="n">
-        <v>6811352</v>
+        <v>6811430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1511,7 +1517,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1548,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125939223</v>
+        <v>125939231</v>
       </c>
       <c r="B11" t="n">
-        <v>79598</v>
+        <v>79422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1565,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454961</v>
+        <v>454930</v>
       </c>
       <c r="R11" t="n">
-        <v>6811450</v>
+        <v>6811482</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125939222</v>
+        <v>125939276</v>
       </c>
       <c r="B12" t="n">
-        <v>79598</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454945</v>
+        <v>454947</v>
       </c>
       <c r="R12" t="n">
-        <v>6811496</v>
+        <v>6811454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1748,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125939250</v>
+        <v>125939260</v>
       </c>
       <c r="B13" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1783,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454931</v>
+        <v>454706</v>
       </c>
       <c r="R13" t="n">
-        <v>6811462</v>
+        <v>6811484</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1802,7 +1808,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1839,32 +1845,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125939253</v>
+        <v>125939262</v>
       </c>
       <c r="B14" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454880</v>
+        <v>454710</v>
       </c>
       <c r="R14" t="n">
-        <v>6811541</v>
+        <v>6811492</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1899,7 +1905,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1936,32 +1942,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125939277</v>
+        <v>125939263</v>
       </c>
       <c r="B15" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1977,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454907</v>
+        <v>454734</v>
       </c>
       <c r="R15" t="n">
-        <v>6811355</v>
+        <v>6811565</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -1996,7 +2002,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2033,32 +2039,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125939243</v>
+        <v>125939264</v>
       </c>
       <c r="B16" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2074,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454896</v>
+        <v>454788</v>
       </c>
       <c r="R16" t="n">
-        <v>6811477</v>
+        <v>6811599</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2093,7 +2099,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2130,32 +2136,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125939230</v>
+        <v>125939265</v>
       </c>
       <c r="B17" t="n">
-        <v>79569</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2171,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454944</v>
+        <v>454793</v>
       </c>
       <c r="R17" t="n">
-        <v>6811441</v>
+        <v>6811562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2190,7 +2196,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2227,32 +2233,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125939280</v>
+        <v>125939266</v>
       </c>
       <c r="B18" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454809</v>
+        <v>454804</v>
       </c>
       <c r="R18" t="n">
-        <v>6811578</v>
+        <v>6811564</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2330,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125939254</v>
+        <v>125939267</v>
       </c>
       <c r="B19" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454943</v>
+        <v>454820</v>
       </c>
       <c r="R19" t="n">
-        <v>6811500</v>
+        <v>6811583</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2384,7 +2390,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2421,50 +2427,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125939238</v>
+        <v>125939268</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454804</v>
+        <v>454882</v>
       </c>
       <c r="R20" t="n">
-        <v>6811564</v>
+        <v>6811551</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2486,7 +2487,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2497,11 +2498,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2528,32 +2524,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125939246</v>
+        <v>125939269</v>
       </c>
       <c r="B21" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454944</v>
+        <v>454964</v>
       </c>
       <c r="R21" t="n">
-        <v>6811441</v>
+        <v>6811440</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2625,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125939283</v>
+        <v>125939270</v>
       </c>
       <c r="B22" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454888</v>
+        <v>454944</v>
       </c>
       <c r="R22" t="n">
-        <v>6811478</v>
+        <v>6811442</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125939285</v>
+        <v>125939271</v>
       </c>
       <c r="B23" t="n">
-        <v>77929</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454930</v>
+        <v>454943</v>
       </c>
       <c r="R23" t="n">
-        <v>6811482</v>
+        <v>6811446</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125939242</v>
+        <v>125939272</v>
       </c>
       <c r="B24" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454883</v>
+        <v>454896</v>
       </c>
       <c r="R24" t="n">
-        <v>6811548</v>
+        <v>6811450</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,14 +2912,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125939262</v>
+        <v>125939273</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2951,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454710</v>
+        <v>454929</v>
       </c>
       <c r="R25" t="n">
-        <v>6811492</v>
+        <v>6811379</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,7 +2972,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3013,14 +3009,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125939263</v>
+        <v>125939274</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3048,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454734</v>
+        <v>454933</v>
       </c>
       <c r="R26" t="n">
-        <v>6811565</v>
+        <v>6811343</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,7 +3069,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3110,50 +3106,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125939233</v>
+        <v>125939275</v>
       </c>
       <c r="B27" t="n">
-        <v>56849</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454794</v>
+        <v>454942</v>
       </c>
       <c r="R27" t="n">
-        <v>6811612</v>
+        <v>6811296</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,7 +3166,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3212,10 +3203,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125939273</v>
+        <v>125939286</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>78730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3223,21 +3214,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3247,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454929</v>
+        <v>454835</v>
       </c>
       <c r="R28" t="n">
-        <v>6811379</v>
+        <v>6811352</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3272,7 +3263,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3309,10 +3300,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125939269</v>
+        <v>125939250</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3320,21 +3311,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3344,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454964</v>
+        <v>454931</v>
       </c>
       <c r="R29" t="n">
-        <v>6811440</v>
+        <v>6811462</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3406,10 +3397,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125939270</v>
+        <v>125939251</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3417,21 +3408,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3441,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454944</v>
+        <v>454806</v>
       </c>
       <c r="R30" t="n">
-        <v>6811442</v>
+        <v>6811636</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,7 +3457,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3503,10 +3494,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125939231</v>
+        <v>125939253</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3514,21 +3505,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3538,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454930</v>
+        <v>454880</v>
       </c>
       <c r="R31" t="n">
-        <v>6811482</v>
+        <v>6811541</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,10 +3591,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125939281</v>
+        <v>125939254</v>
       </c>
       <c r="B32" t="n">
-        <v>78647</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3602,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454865</v>
+        <v>454943</v>
       </c>
       <c r="R32" t="n">
-        <v>6811503</v>
+        <v>6811500</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,7 +3651,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3697,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125939224</v>
+        <v>125939256</v>
       </c>
       <c r="B33" t="n">
-        <v>79598</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454899</v>
+        <v>454960</v>
       </c>
       <c r="R33" t="n">
-        <v>6811425</v>
+        <v>6811451</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125939221</v>
+        <v>125939257</v>
       </c>
       <c r="B34" t="n">
-        <v>79598</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454868</v>
+        <v>454910</v>
       </c>
       <c r="R34" t="n">
-        <v>6811496</v>
+        <v>6811442</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3854,7 +3845,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3891,10 +3882,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125939228</v>
+        <v>125939217</v>
       </c>
       <c r="B35" t="n">
-        <v>79569</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3902,21 +3893,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3926,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454892</v>
+        <v>454837</v>
       </c>
       <c r="R35" t="n">
-        <v>6811478</v>
+        <v>6811351</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3951,7 +3942,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3988,10 +3979,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125939245</v>
+        <v>125939218</v>
       </c>
       <c r="B36" t="n">
-        <v>78739</v>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3990,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4014,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454945</v>
+        <v>454769</v>
       </c>
       <c r="R36" t="n">
-        <v>6811496</v>
+        <v>6811673</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4048,7 +4039,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4085,10 +4076,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125939241</v>
+        <v>125939219</v>
       </c>
       <c r="B37" t="n">
-        <v>78739</v>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4087,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4111,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454802</v>
+        <v>454849</v>
       </c>
       <c r="R37" t="n">
-        <v>6811558</v>
+        <v>6811570</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,10 +4173,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125939279</v>
+        <v>125939221</v>
       </c>
       <c r="B38" t="n">
-        <v>78647</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4193,21 +4184,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454802</v>
+        <v>454868</v>
       </c>
       <c r="R38" t="n">
-        <v>6811557</v>
+        <v>6811496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,10 +4270,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125939218</v>
+        <v>125939222</v>
       </c>
       <c r="B39" t="n">
-        <v>79598</v>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4314,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454769</v>
+        <v>454945</v>
       </c>
       <c r="R39" t="n">
-        <v>6811673</v>
+        <v>6811496</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4339,7 +4330,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4376,10 +4367,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125939274</v>
+        <v>125939223</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4378,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4402,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454933</v>
+        <v>454961</v>
       </c>
       <c r="R40" t="n">
-        <v>6811343</v>
+        <v>6811450</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,10 +4464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125939265</v>
+        <v>125939224</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4475,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454793</v>
+        <v>454899</v>
       </c>
       <c r="R41" t="n">
-        <v>6811562</v>
+        <v>6811425</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4533,7 +4524,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4570,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125939226</v>
+        <v>125939225</v>
       </c>
       <c r="B42" t="n">
-        <v>79598</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4605,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454938</v>
+        <v>454951</v>
       </c>
       <c r="R42" t="n">
-        <v>6811337</v>
+        <v>6811384</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,10 +4658,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125939266</v>
+        <v>125939226</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4678,21 +4669,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4702,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454804</v>
+        <v>454938</v>
       </c>
       <c r="R43" t="n">
-        <v>6811564</v>
+        <v>6811337</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4727,7 +4718,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -4764,10 +4755,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125939227</v>
+        <v>125939285</v>
       </c>
       <c r="B44" t="n">
-        <v>79569</v>
+        <v>78334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4775,21 +4766,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4799,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454868</v>
+        <v>454930</v>
       </c>
       <c r="R44" t="n">
-        <v>6811501</v>
+        <v>6811482</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4824,7 +4815,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -4861,10 +4852,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125939219</v>
+        <v>125939238</v>
       </c>
       <c r="B45" t="n">
-        <v>79598</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4872,34 +4863,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454849</v>
+        <v>454804</v>
       </c>
       <c r="R45" t="n">
-        <v>6811570</v>
+        <v>6811564</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4932,6 +4928,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4958,45 +4959,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125939264</v>
+        <v>125939233</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>57141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>St. Skidbågåsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454788</v>
+        <v>454794</v>
       </c>
       <c r="R46" t="n">
-        <v>6811599</v>
+        <v>6811612</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5055,10 +5061,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125939257</v>
+        <v>125939240</v>
       </c>
       <c r="B47" t="n">
-        <v>78738</v>
+        <v>79085</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5066,21 +5072,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5090,10 +5096,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454910</v>
+        <v>454806</v>
       </c>
       <c r="R47" t="n">
-        <v>6811442</v>
+        <v>6811636</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5115,7 +5121,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5152,10 +5158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125939229</v>
+        <v>125939241</v>
       </c>
       <c r="B48" t="n">
-        <v>79569</v>
+        <v>79085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5163,21 +5169,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5187,10 +5193,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454945</v>
+        <v>454802</v>
       </c>
       <c r="R48" t="n">
-        <v>6811496</v>
+        <v>6811558</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5212,7 +5218,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5249,10 +5255,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125939284</v>
+        <v>125939242</v>
       </c>
       <c r="B49" t="n">
-        <v>78647</v>
+        <v>79085</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5260,21 +5266,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5290,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454896</v>
+        <v>454883</v>
       </c>
       <c r="R49" t="n">
-        <v>6811430</v>
+        <v>6811548</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5346,10 +5352,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125939225</v>
+        <v>125939243</v>
       </c>
       <c r="B50" t="n">
-        <v>79598</v>
+        <v>79085</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5357,21 +5363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454951</v>
+        <v>454896</v>
       </c>
       <c r="R50" t="n">
-        <v>6811384</v>
+        <v>6811477</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5443,10 +5449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125939267</v>
+        <v>125939245</v>
       </c>
       <c r="B51" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5454,21 +5460,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5478,10 +5484,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454820</v>
+        <v>454945</v>
       </c>
       <c r="R51" t="n">
-        <v>6811583</v>
+        <v>6811496</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5503,7 +5509,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -5540,10 +5546,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125939260</v>
+        <v>125939246</v>
       </c>
       <c r="B52" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5551,21 +5557,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5575,10 +5581,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454706</v>
+        <v>454944</v>
       </c>
       <c r="R52" t="n">
-        <v>6811484</v>
+        <v>6811441</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5600,7 +5606,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5637,10 +5643,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125939251</v>
+        <v>125939247</v>
       </c>
       <c r="B53" t="n">
-        <v>78738</v>
+        <v>79085</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5648,21 +5654,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5672,10 +5678,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454806</v>
+        <v>454910</v>
       </c>
       <c r="R53" t="n">
-        <v>6811636</v>
+        <v>6811441</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5697,7 +5703,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5734,10 +5740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125939271</v>
+        <v>125939248</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5745,21 +5751,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5769,10 +5775,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454943</v>
+        <v>454938</v>
       </c>
       <c r="R54" t="n">
-        <v>6811446</v>
+        <v>6811339</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5831,10 +5837,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125939268</v>
+        <v>125939227</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79917</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5842,21 +5848,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5866,10 +5872,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454882</v>
+        <v>454868</v>
       </c>
       <c r="R55" t="n">
-        <v>6811551</v>
+        <v>6811501</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5891,7 +5897,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -5928,10 +5934,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125939248</v>
+        <v>125939228</v>
       </c>
       <c r="B56" t="n">
-        <v>78739</v>
+        <v>79917</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5939,21 +5945,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5963,10 +5969,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454938</v>
+        <v>454892</v>
       </c>
       <c r="R56" t="n">
-        <v>6811339</v>
+        <v>6811478</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6025,32 +6031,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125939232</v>
+        <v>125939229</v>
       </c>
       <c r="B57" t="n">
-        <v>91530</v>
+        <v>79917</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>71</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6060,10 +6066,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>454788</v>
+        <v>454945</v>
       </c>
       <c r="R57" t="n">
-        <v>6811611</v>
+        <v>6811496</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6085,7 +6091,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -6098,18 +6104,12 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Behöver mikroskoperas</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6125,6 +6125,103 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125939230</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>St. Skidbågåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>454944</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6811441</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23535-2025 artfynd.xlsx
+++ b/artfynd/A 23535-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939232</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939277</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939278</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1066,6 +1086,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939279</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1163,6 +1188,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939280</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939281</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1357,6 +1392,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939282</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1454,6 +1494,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939283</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1551,6 +1596,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939284</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1648,6 +1698,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939231</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1745,6 +1800,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939276</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1842,6 +1902,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939260</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1939,6 +2004,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939262</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2036,6 +2106,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939263</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2133,6 +2208,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939264</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2230,6 +2310,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939265</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2327,6 +2412,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939266</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2424,6 +2514,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939267</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2521,6 +2616,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939268</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2618,6 +2718,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939269</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2715,6 +2820,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939270</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2812,6 +2922,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939271</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2909,6 +3024,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939272</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3006,6 +3126,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939273</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3103,6 +3228,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939274</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3200,6 +3330,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939275</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3297,6 +3432,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939286</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3394,6 +3534,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939250</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3491,6 +3636,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939251</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3588,6 +3738,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939253</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3685,6 +3840,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939254</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3782,6 +3942,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939256</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3879,6 +4044,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939257</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3976,6 +4146,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939217</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4073,6 +4248,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939218</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4170,6 +4350,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939219</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4267,6 +4452,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939221</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4364,6 +4554,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939222</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4461,6 +4656,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939223</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4558,6 +4758,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939224</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4655,6 +4860,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939225</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4752,6 +4962,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939226</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4849,6 +5064,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939285</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4956,6 +5176,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939238</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5058,6 +5283,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939233</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5155,6 +5385,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939240</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5252,6 +5487,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939241</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5349,6 +5589,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939242</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5446,6 +5691,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939243</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5543,6 +5793,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939245</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5640,6 +5895,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939246</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5737,6 +5997,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939247</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5834,6 +6099,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939248</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5931,6 +6201,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939227</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6028,6 +6303,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939228</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6125,6 +6405,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939229</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6222,8 +6507,72 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939230</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>